--- a/data/excel/competency_assessors.xlsx
+++ b/data/excel/competency_assessors.xlsx
@@ -442,12 +442,12 @@
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t>Erwin Yap Almine</t>
+          <t>Arnaldo Binalangbang Salem</t>
         </is>
       </c>
       <c t="inlineStr" r="D4">
         <is>
-          <t>Brgy. Nueva Esperanza Hinunangan Southern Leyte</t>
+          <t>Tigbao Libagon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E4">
@@ -457,47 +457,47 @@
       </c>
       <c t="inlineStr" r="F4">
         <is>
-          <t>4/25/1988</t>
+          <t>6/5/1981</t>
         </is>
       </c>
       <c t="inlineStr" r="G4">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t>Trainer</t>
+          <t>Farm Owner/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I4">
         <is>
-          <t>Acedilla Technogical Institute - St. Bernard</t>
+          <t>A.i Integrated Farm School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K4">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Rice Machinery Operations NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L4">
         <is>
-          <t>CA-EIM0208642327002</t>
+          <t>CA-RMO0208642326007</t>
         </is>
       </c>
       <c t="inlineStr" r="M4">
         <is>
-          <t>3/15/2023</t>
+          <t>6/30/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N4">
         <is>
-          <t>3/23/2027</t>
+          <t>11/18/2026</t>
         </is>
       </c>
     </row>
@@ -514,12 +514,12 @@
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t>Roger . Ladica .</t>
+          <t>Kierzner Dounee Ordiz Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D5">
         <is>
-          <t>Ponong Bato Leyte</t>
+          <t>Mambajao City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E5">
@@ -529,47 +529,47 @@
       </c>
       <c t="inlineStr" r="F5">
         <is>
-          <t>3/2/1976</t>
+          <t>3/30/1996</t>
         </is>
       </c>
       <c t="inlineStr" r="G5">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t>Trainer</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I5">
         <is>
-          <t>On-call</t>
+          <t>Private/on-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Human Health / Health Care</t>
         </is>
       </c>
       <c t="inlineStr" r="K5">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Caregiving NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L5">
         <is>
-          <t>CA-EAW0108642328004</t>
+          <t>CA-CGV0208642326015</t>
         </is>
       </c>
       <c t="inlineStr" r="M5">
         <is>
-          <t>3/17/2023</t>
+          <t>11/3/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N5">
         <is>
-          <t>1/11/2028</t>
+          <t>11/29/2026</t>
         </is>
       </c>
     </row>
@@ -586,12 +586,12 @@
       </c>
       <c t="inlineStr" r="C6">
         <is>
-          <t>Arnaldo Binalangbang Salem</t>
+          <t>Harris Zabala Aguilando</t>
         </is>
       </c>
       <c t="inlineStr" r="D6">
         <is>
-          <t>Tigbao Libagon Southern Leyte</t>
+          <t>Las Navas Northern Samar</t>
         </is>
       </c>
       <c t="inlineStr" r="E6">
@@ -601,7 +601,7 @@
       </c>
       <c t="inlineStr" r="F6">
         <is>
-          <t>6/5/1981</t>
+          <t>8/23/1977</t>
         </is>
       </c>
       <c t="inlineStr" r="G6">
@@ -611,12 +611,12 @@
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t>Farm Owner/assessor</t>
+          <t>Sr. Tesd Specialist</t>
         </is>
       </c>
       <c t="inlineStr" r="I6">
         <is>
-          <t>A.i Integrated Farm School, Inc.</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
@@ -626,22 +626,22 @@
       </c>
       <c t="inlineStr" r="K6">
         <is>
-          <t>Organic Agriculture Production NC II</t>
+          <t>Animal Production (Ruminants) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L6">
         <is>
-          <t>CA-OAP0208642328006</t>
+          <t>AFFAPR21302086425260010</t>
         </is>
       </c>
       <c t="inlineStr" r="M6">
         <is>
-          <t>6/30/2023</t>
+          <t>8/22/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N6">
         <is>
-          <t>3/28/2028</t>
+          <t>11/30/2026</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t>Arnaldo Binalangbang Salem</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D7">
         <is>
-          <t>Tigbao Libagon Southern Leyte</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E7">
@@ -673,7 +673,7 @@
       </c>
       <c t="inlineStr" r="F7">
         <is>
-          <t>6/5/1981</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G7">
@@ -681,39 +681,29 @@
           <t>College Graduate</t>
         </is>
       </c>
-      <c t="inlineStr" r="H7">
-        <is>
-          <t>Farm Owner/assessor</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I7">
-        <is>
-          <t>A.i Integrated Farm School, Inc.</t>
-        </is>
-      </c>
       <c t="inlineStr" r="J7">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>TVET</t>
         </is>
       </c>
       <c t="inlineStr" r="K7">
         <is>
-          <t>Rice Machinery Operations NC II</t>
+          <t>Trainers Methodology Level  NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L7">
         <is>
-          <t>CA-RMO0208642326007</t>
+          <t>TVETRM11101000025260282</t>
         </is>
       </c>
       <c t="inlineStr" r="M7">
         <is>
-          <t>6/30/2023</t>
+          <t>12/6/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N7">
         <is>
-          <t>11/18/2026</t>
+          <t>12/5/2026</t>
         </is>
       </c>
     </row>
@@ -730,57 +720,62 @@
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t>Cerecio Cabudbud Mendoza</t>
+          <t>Marian Ichon Angub</t>
         </is>
       </c>
       <c t="inlineStr" r="D8">
         <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
+          <t>Punong,  Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F8">
         <is>
-          <t>2/21/1960</t>
+          <t>9/20/1992</t>
         </is>
       </c>
       <c t="inlineStr" r="G8">
         <is>
-          <t>Masteral</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t>Retired School Head Teacher/on Call Trainer/assessor</t>
+          <t>Competency Assessor</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I8">
+        <is>
+          <t>Sir G.  Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K8">
         <is>
-          <t>Driving NC II</t>
+          <t>Organic Agriculture Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L8">
         <is>
-          <t>CA-DRV0208642328008</t>
+          <t>CA-OAP0208642427009</t>
         </is>
       </c>
       <c t="inlineStr" r="M8">
         <is>
-          <t>6/30/2023</t>
+          <t>2/28/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N8">
         <is>
-          <t>4/2/2028</t>
+          <t>2/10/2027</t>
         </is>
       </c>
     </row>
@@ -797,12 +792,12 @@
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t>Cerecio Cabudbud Mendoza</t>
+          <t>Erwin Yap Almine</t>
         </is>
       </c>
       <c t="inlineStr" r="D9">
         <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
+          <t>Brgy. Nueva Esperanza Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E9">
@@ -812,42 +807,47 @@
       </c>
       <c t="inlineStr" r="F9">
         <is>
-          <t>2/21/1960</t>
+          <t>4/25/1988</t>
         </is>
       </c>
       <c t="inlineStr" r="G9">
         <is>
-          <t>Masteral</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t>Retired School Head Teacher/on Call Trainer/assessor</t>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I9">
+        <is>
+          <t>Acedilla Technogical Institute - St. Bernard</t>
         </is>
       </c>
       <c t="inlineStr" r="J9">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K9">
         <is>
-          <t>Driving (Passenger Bus/Straight Truck) NC III</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L9">
         <is>
-          <t>CA-DRB0308642326009</t>
+          <t>CA-EIM0208642327002</t>
         </is>
       </c>
       <c t="inlineStr" r="M9">
         <is>
-          <t>6/30/2023</t>
+          <t>3/15/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N9">
         <is>
-          <t>10/18/2026</t>
+          <t>3/23/2027</t>
         </is>
       </c>
     </row>
@@ -864,22 +864,22 @@
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t>Rhett Togonon Binghoy</t>
+          <t>Michel Tingcoy Pata</t>
         </is>
       </c>
       <c t="inlineStr" r="D10">
         <is>
-          <t>Salog Hinunangan Southern Leyte</t>
+          <t>Mahayahay Bontoc Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F10">
         <is>
-          <t>2/24/1979</t>
+          <t>8/24/1980</t>
         </is>
       </c>
       <c t="inlineStr" r="G10">
@@ -889,37 +889,37 @@
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t>Assessor</t>
+          <t>Teacher 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
         <is>
-          <t>Pacific Vocational Training Center, Inc.</t>
+          <t>Villa Jacinta National Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Garments</t>
         </is>
       </c>
       <c t="inlineStr" r="K10">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
+          <t>Dressmaking NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L10">
         <is>
-          <t>CA-EAW0208642328012</t>
+          <t>GRMDRM20502086426270004</t>
         </is>
       </c>
       <c t="inlineStr" r="M10">
         <is>
-          <t>8/3/2023</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N10">
         <is>
-          <t>5/4/2028</t>
+          <t>5/3/2027</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t>Ricky Zafra Tapal</t>
+          <t>Edsel Ray Bactul Vallinas</t>
         </is>
       </c>
       <c t="inlineStr" r="D11">
         <is>
-          <t>Baranggay Salog,  Hinunangan Southern Leyte</t>
+          <t>440, I. Paler St.(ext) Tagnipa City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E11">
@@ -951,7 +951,7 @@
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t>1/12/1985</t>
+          <t>12/15/1998</t>
         </is>
       </c>
       <c t="inlineStr" r="G11">
@@ -961,37 +961,37 @@
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Special Science Teacher I</t>
         </is>
       </c>
       <c t="inlineStr" r="I11">
         <is>
-          <t>N/a</t>
+          <t>Maasin City National High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J11">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K11">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Computer Systems Servicing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L11">
         <is>
-          <t>CA-EAW0108642328013</t>
+          <t>ELCCSS21302086426270020</t>
         </is>
       </c>
       <c t="inlineStr" r="M11">
         <is>
-          <t>8/3/2023</t>
+          <t>6/8/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N11">
         <is>
-          <t>6/22/2028</t>
+          <t>10/27/2027</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c t="inlineStr" r="C12">
         <is>
-          <t>Ricky Zafra Tapal</t>
+          <t>Amiel Lora Bosque</t>
         </is>
       </c>
       <c t="inlineStr" r="D12">
         <is>
-          <t>Baranggay Salog,  Hinunangan Southern Leyte</t>
+          <t>Brgy. San Rafael City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E12">
@@ -1023,12 +1023,12 @@
       </c>
       <c t="inlineStr" r="F12">
         <is>
-          <t>1/12/1985</t>
+          <t>10/11/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G12">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H12">
@@ -1038,7 +1038,7 @@
       </c>
       <c t="inlineStr" r="I12">
         <is>
-          <t>N/a</t>
+          <t>St. Thomas Aquinas College, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J12">
@@ -1048,22 +1048,22 @@
       </c>
       <c t="inlineStr" r="K12">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L12">
         <is>
-          <t>CA-EAW0208642328014</t>
+          <t>CA-EAW0108642427004</t>
         </is>
       </c>
       <c t="inlineStr" r="M12">
         <is>
-          <t>8/3/2023</t>
+          <t>2/26/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N12">
         <is>
-          <t>2/6/2028</t>
+          <t>11/10/2027</t>
         </is>
       </c>
     </row>
@@ -1080,22 +1080,22 @@
       </c>
       <c t="inlineStr" r="C13">
         <is>
-          <t>Kierzner Dounee Ordiz Caores</t>
+          <t>Lerma Caña Parado</t>
         </is>
       </c>
       <c t="inlineStr" r="D13">
         <is>
-          <t>Mambajao City of Maasin Southern Leyte</t>
+          <t>Real Street Poblacion Julita Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F13">
         <is>
-          <t>3/30/1996</t>
+          <t>1/24/1978</t>
         </is>
       </c>
       <c t="inlineStr" r="G13">
@@ -1110,32 +1110,32 @@
       </c>
       <c t="inlineStr" r="I13">
         <is>
-          <t>Private/on-call</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
         <is>
-          <t>Human Health / Health Care</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K13">
         <is>
-          <t>Caregiving NC II</t>
+          <t>Agroentrepreneurship NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L13">
         <is>
-          <t>CA-CGV0208642326015</t>
+          <t>CA-AGE0208642427005</t>
         </is>
       </c>
       <c t="inlineStr" r="M13">
         <is>
-          <t>11/3/2023</t>
+          <t>2/26/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N13">
         <is>
-          <t>11/29/2026</t>
+          <t>12/7/2027</t>
         </is>
       </c>
     </row>
@@ -1152,62 +1152,62 @@
       </c>
       <c t="inlineStr" r="C14">
         <is>
-          <t>Ghubert Fedival Francisco</t>
+          <t>Ma. Asuncion Bagolor Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D14">
         <is>
-          <t>Brgy. 91 Abucay Tacloban City Leyte</t>
+          <t>Brgy. Dongon City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F14">
         <is>
-          <t>6/28/1976</t>
+          <t>8/10/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G14">
         <is>
-          <t>Doctorate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t>Trainer/competency Assessor</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I14">
         <is>
-          <t>Ghrace Jhoy Integrated Farm</t>
+          <t>The College Of Maasin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K14">
         <is>
-          <t>Agricultural Crops Production NC II</t>
+          <t>Bread and Pastry Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L14">
         <is>
-          <t>CA-ACP0208642328017</t>
+          <t>CA-BPP0208642428010</t>
         </is>
       </c>
       <c t="inlineStr" r="M14">
         <is>
-          <t>11/28/2023</t>
+          <t>2/28/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N14">
         <is>
-          <t>5/25/2028</t>
+          <t>1/8/2028</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Roger . Ladica .</t>
         </is>
       </c>
       <c t="inlineStr" r="D15">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>Ponong Bato Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E15">
@@ -1239,47 +1239,47 @@
       </c>
       <c t="inlineStr" r="F15">
         <is>
-          <t>10/13/1993</t>
+          <t>3/2/1976</t>
         </is>
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t>Trainer/competency Assessor</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I15">
         <is>
-          <t>Ghrace Jhoy Integrated Farm</t>
+          <t>On-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K15">
         <is>
-          <t>Agricultural Crops Production NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L15">
         <is>
-          <t>CA-ACP0208642328018</t>
+          <t>CA-EAW0108642328004</t>
         </is>
       </c>
       <c t="inlineStr" r="M15">
         <is>
-          <t>11/28/2023</t>
+          <t>3/17/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N15">
         <is>
-          <t>5/25/2028</t>
+          <t>1/11/2028</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c t="inlineStr" r="C16">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Ricky Zafra Tapal</t>
         </is>
       </c>
       <c t="inlineStr" r="D16">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Baranggay Salog,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E16">
@@ -1311,47 +1311,47 @@
       </c>
       <c t="inlineStr" r="F16">
         <is>
-          <t>4/7/1969</t>
+          <t>1/12/1985</t>
         </is>
       </c>
       <c t="inlineStr" r="G16">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t>Competency Assessor</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I16">
         <is>
-          <t>On-call (private)</t>
+          <t>N/a</t>
         </is>
       </c>
       <c t="inlineStr" r="J16">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K16">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L16">
         <is>
-          <t>CA-EIM0208642328016</t>
+          <t>CA-EAW0208642328014</t>
         </is>
       </c>
       <c t="inlineStr" r="M16">
         <is>
-          <t>11/28/2023</t>
+          <t>8/3/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N16">
         <is>
-          <t>9/24/2028</t>
+          <t>2/6/2028</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c t="inlineStr" r="C17">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Arnaldo Binalangbang Salem</t>
         </is>
       </c>
       <c t="inlineStr" r="D17">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Tigbao Libagon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E17">
@@ -1383,22 +1383,22 @@
       </c>
       <c t="inlineStr" r="F17">
         <is>
-          <t>4/7/1969</t>
+          <t>6/5/1981</t>
         </is>
       </c>
       <c t="inlineStr" r="G17">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t>Competency Assessor</t>
+          <t>Farm Owner/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I17">
         <is>
-          <t>Liz Integrated Farm</t>
+          <t>A.i Integrated Farm School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
@@ -1413,17 +1413,17 @@
       </c>
       <c t="inlineStr" r="L17">
         <is>
-          <t>CA-OAP0208642328019</t>
+          <t>CA-OAP0208642328006</t>
         </is>
       </c>
       <c t="inlineStr" r="M17">
         <is>
-          <t>11/30/2023</t>
+          <t>6/30/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N17">
         <is>
-          <t>5/15/2028</t>
+          <t>3/28/2028</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c t="inlineStr" r="C18">
         <is>
-          <t>Kierzner Dounee Ordiz Caores</t>
+          <t>Cerecio Cabudbud Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D18">
         <is>
-          <t>Mambajao City of Maasin Southern Leyte</t>
+          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E18">
@@ -1455,47 +1455,42 @@
       </c>
       <c t="inlineStr" r="F18">
         <is>
-          <t>3/30/1996</t>
+          <t>2/21/1960</t>
         </is>
       </c>
       <c t="inlineStr" r="G18">
         <is>
-          <t>College Graduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t>Competency Assessor</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I18">
-        <is>
-          <t>On-call</t>
+          <t>Retired School Head Teacher/on Call Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
         <is>
-          <t>Human Health / Health Care</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K18">
         <is>
-          <t>Health Care Services NC II</t>
+          <t>Driving NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L18">
         <is>
-          <t>CA-HCS0208642429001</t>
+          <t>CA-DRV0208642328008</t>
         </is>
       </c>
       <c t="inlineStr" r="M18">
         <is>
-          <t>1/5/2024</t>
+          <t>6/30/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N18">
         <is>
-          <t>1/3/2029</t>
+          <t>4/2/2028</t>
         </is>
       </c>
     </row>
@@ -1512,22 +1507,22 @@
       </c>
       <c t="inlineStr" r="C19">
         <is>
-          <t>Lerma Caña Parado</t>
+          <t>Michael Mostaza Diaz</t>
         </is>
       </c>
       <c t="inlineStr" r="D19">
         <is>
-          <t>Real Street Poblacion Julita Leyte</t>
+          <t>76 A. Luna Street  City of Baybay Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E19">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F19">
         <is>
-          <t>1/24/1978</t>
+          <t>4/24/1985</t>
         </is>
       </c>
       <c t="inlineStr" r="G19">
@@ -1542,7 +1537,7 @@
       </c>
       <c t="inlineStr" r="I19">
         <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
+          <t>Freelancer</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
@@ -1557,17 +1552,17 @@
       </c>
       <c t="inlineStr" r="L19">
         <is>
-          <t>CA-EVM0308642428002</t>
+          <t>CA-EVM0308642328010</t>
         </is>
       </c>
       <c t="inlineStr" r="M19">
         <is>
-          <t>1/5/2024</t>
+          <t>6/30/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N19">
         <is>
-          <t>6/29/2028</t>
+          <t>4/16/2028</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1579,12 @@
       </c>
       <c t="inlineStr" r="C20">
         <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
+          <t>Rhett Togonon Binghoy</t>
         </is>
       </c>
       <c t="inlineStr" r="D20">
         <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
+          <t>Salog Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E20">
@@ -1599,22 +1594,22 @@
       </c>
       <c t="inlineStr" r="F20">
         <is>
-          <t>6/26/1983</t>
+          <t>2/24/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G20">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I20">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>Pacific Vocational Training Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
@@ -1624,22 +1619,22 @@
       </c>
       <c t="inlineStr" r="K20">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L20">
         <is>
-          <t>CA-EAW0108642428003</t>
+          <t>CA-EAW0208642328012</t>
         </is>
       </c>
       <c t="inlineStr" r="M20">
         <is>
-          <t>1/5/2024</t>
+          <t>8/3/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N20">
         <is>
-          <t>11/15/2028</t>
+          <t>5/4/2028</t>
         </is>
       </c>
     </row>
@@ -1656,27 +1651,27 @@
       </c>
       <c t="inlineStr" r="C21">
         <is>
-          <t>Lerma Caña Parado</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D21">
         <is>
-          <t>Real Street Poblacion Julita Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E21">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t>1/24/1978</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G21">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H21">
@@ -1686,7 +1681,7 @@
       </c>
       <c t="inlineStr" r="I21">
         <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
+          <t>Liz Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J21">
@@ -1696,22 +1691,22 @@
       </c>
       <c t="inlineStr" r="K21">
         <is>
-          <t>Agroentrepreneurship NC II</t>
+          <t>Organic Agriculture Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L21">
         <is>
-          <t>CA-AGE0208642427005</t>
+          <t>CA-OAP0208642328019</t>
         </is>
       </c>
       <c t="inlineStr" r="M21">
         <is>
-          <t>2/26/2024</t>
+          <t>11/30/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N21">
         <is>
-          <t>12/7/2027</t>
+          <t>5/15/2028</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1723,12 @@
       </c>
       <c t="inlineStr" r="C22">
         <is>
-          <t>Amiel Lora Bosque</t>
+          <t>Marven Dejarme Estinozo</t>
         </is>
       </c>
       <c t="inlineStr" r="D22">
         <is>
-          <t>Brgy. San Rafael City of Maasin Southern Leyte</t>
+          <t>Brgy. Consolacion Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E22">
@@ -1743,47 +1738,47 @@
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t>10/11/1983</t>
+          <t>1/3/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G22">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Head Computer Technician</t>
         </is>
       </c>
       <c t="inlineStr" r="I22">
         <is>
-          <t>St. Thomas Aquinas College, Inc.</t>
+          <t>Arc Tutorials Learning Services Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K22">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Computer Systems Servicing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L22">
         <is>
-          <t>CA-EAW0108642427004</t>
+          <t>ELCCSS21302086424280008</t>
         </is>
       </c>
       <c t="inlineStr" r="M22">
         <is>
-          <t>2/26/2024</t>
+          <t>10/24/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N22">
         <is>
-          <t>11/10/2027</t>
+          <t>5/18/2028</t>
         </is>
       </c>
     </row>
@@ -1800,62 +1795,62 @@
       </c>
       <c t="inlineStr" r="C23">
         <is>
-          <t>Maria Normida Ordiz Caores</t>
+          <t>Cerecio Cabudbud Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D23">
         <is>
-          <t>R. Kangleon Street Brgy. Mambajao,  City of Maasin Southern Leyte</t>
+          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E23">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t>12/6/1969</t>
+          <t>2/21/1960</t>
         </is>
       </c>
       <c t="inlineStr" r="G23">
         <is>
-          <t>College Undergraduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t>Competency Assessor</t>
+          <t>Maintenance Head</t>
         </is>
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
+          <t>Ghrace Jhoy Technical And Vocational School</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K23">
         <is>
-          <t>Cookery NC II</t>
+          <t>Plumbing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L23">
         <is>
-          <t>CA-COK0208642429006</t>
+          <t>CONPLM21402086426280024</t>
         </is>
       </c>
       <c t="inlineStr" r="M23">
         <is>
-          <t>2/26/2024</t>
+          <t>9/2/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N23">
         <is>
-          <t>2/22/2029</t>
+          <t>5/24/2028</t>
         </is>
       </c>
     </row>
@@ -1897,37 +1892,37 @@
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Trainer/competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
+          <t>Ghrace Jhoy Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
         <is>
-          <t>Social, Community Development and Other Services</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K24">
         <is>
-          <t>Bookkeeping NC III</t>
+          <t>Agricultural Crops Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L24">
         <is>
-          <t>CA-BKP0308642428007</t>
+          <t>CA-ACP0208642328017</t>
         </is>
       </c>
       <c t="inlineStr" r="M24">
         <is>
-          <t>2/26/2024</t>
+          <t>11/28/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N24">
         <is>
-          <t>12/21/2028</t>
+          <t>5/25/2028</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1939,12 @@
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t>Kierzner Dounee Ordiz Caores</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D25">
         <is>
-          <t>Mambajao City of Maasin Southern Leyte</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E25">
@@ -1959,7 +1954,7 @@
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t>3/30/1996</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G25">
@@ -1969,37 +1964,37 @@
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t>Competency Assessor</t>
+          <t>Trainer/competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
         <is>
-          <t>On-call</t>
+          <t>Ghrace Jhoy Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K25">
         <is>
-          <t>Driving NC II</t>
+          <t>Agricultural Crops Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L25">
         <is>
-          <t>CA-DRV0208642426008</t>
+          <t>CA-ACP0208642328018</t>
         </is>
       </c>
       <c t="inlineStr" r="M25">
         <is>
-          <t>2/28/2024</t>
+          <t>11/28/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N25">
         <is>
-          <t>10/20/2026</t>
+          <t>5/25/2028</t>
         </is>
       </c>
     </row>
@@ -2016,27 +2011,27 @@
       </c>
       <c t="inlineStr" r="C26">
         <is>
-          <t>Ma. Asuncion Bagolor Mendoza</t>
+          <t>Ricky Zafra Tapal</t>
         </is>
       </c>
       <c t="inlineStr" r="D26">
         <is>
-          <t>Brgy. Dongon City of Maasin Southern Leyte</t>
+          <t>Baranggay Salog,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t>8/10/1979</t>
+          <t>1/12/1985</t>
         </is>
       </c>
       <c t="inlineStr" r="G26">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H26">
@@ -2046,32 +2041,32 @@
       </c>
       <c t="inlineStr" r="I26">
         <is>
-          <t>The College Of Maasin, Inc.</t>
+          <t>N/a</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K26">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L26">
         <is>
-          <t>CA-BPP0208642428010</t>
+          <t>CA-EAW0108642328013</t>
         </is>
       </c>
       <c t="inlineStr" r="M26">
         <is>
-          <t>2/28/2024</t>
+          <t>8/3/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N26">
         <is>
-          <t>1/8/2028</t>
+          <t>6/22/2028</t>
         </is>
       </c>
     </row>
@@ -2088,22 +2083,22 @@
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t>Gaudencio Regaton Saratan Jr.</t>
+          <t>Carmelyn Oppus Liberato</t>
         </is>
       </c>
       <c t="inlineStr" r="D27">
         <is>
-          <t>168 Rosales Street Brgy. Tagnipa City of Maasin Southern Leyte</t>
+          <t>Brgy. Maanyag  Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t>6/14/1969</t>
+          <t>1/8/1998</t>
         </is>
       </c>
       <c t="inlineStr" r="G27">
@@ -2113,37 +2108,37 @@
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I27">
         <is>
-          <t>On-call</t>
+          <t>Ghrace Joy Technical And Vocational School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K27">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Food and Beverage Services NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L27">
         <is>
-          <t>CA-EIM0208642428011</t>
+          <t>TRSFBS21302086426280010</t>
         </is>
       </c>
       <c t="inlineStr" r="M27">
         <is>
-          <t>2/28/2024</t>
+          <t>2/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N27">
         <is>
-          <t>8/24/2028</t>
+          <t>6/28/2028</t>
         </is>
       </c>
     </row>
@@ -2160,62 +2155,62 @@
       </c>
       <c t="inlineStr" r="C28">
         <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
+          <t>Lerma Caña Parado</t>
         </is>
       </c>
       <c t="inlineStr" r="D28">
         <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
+          <t>Real Street Poblacion Julita Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E28">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F28">
         <is>
-          <t>6/26/1983</t>
+          <t>1/24/1978</t>
         </is>
       </c>
       <c t="inlineStr" r="G28">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H28">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I28">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J28">
         <is>
-          <t>Construction</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K28">
         <is>
-          <t>PV Systems Installation NC II</t>
+          <t>Events Management Services NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L28">
         <is>
-          <t>CA-PVI0208642428012</t>
+          <t>CA-EVM0308642428002</t>
         </is>
       </c>
       <c t="inlineStr" r="M28">
         <is>
-          <t>2/28/2024</t>
+          <t>1/5/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N28">
         <is>
-          <t>10/12/2028</t>
+          <t>6/29/2028</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2227,12 @@
       </c>
       <c t="inlineStr" r="C29">
         <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
+          <t>Gaudencio Regaton Saratan Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D29">
         <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
+          <t>168 Rosales Street Brgy. Tagnipa City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E29">
@@ -2247,12 +2242,12 @@
       </c>
       <c t="inlineStr" r="F29">
         <is>
-          <t>6/26/1983</t>
+          <t>6/14/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G29">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H29">
@@ -2262,32 +2257,32 @@
       </c>
       <c t="inlineStr" r="I29">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>On-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J29">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K29">
         <is>
-          <t>Driving (Passenger Bus/Straight Truck) NC III</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L29">
         <is>
-          <t>CA-DRB0308642426017</t>
+          <t>CA-EIM0208642428011</t>
         </is>
       </c>
       <c t="inlineStr" r="M29">
         <is>
-          <t>2/29/2024</t>
+          <t>2/28/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N29">
         <is>
-          <t>9/15/2026</t>
+          <t>8/24/2028</t>
         </is>
       </c>
     </row>
@@ -2304,27 +2299,27 @@
       </c>
       <c t="inlineStr" r="C30">
         <is>
-          <t>Marian Ichon Angub</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D30">
         <is>
-          <t>Punong,  Tomas Oppus Southern Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E30">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F30">
         <is>
-          <t>9/20/1992</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G30">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H30">
@@ -2334,32 +2329,32 @@
       </c>
       <c t="inlineStr" r="I30">
         <is>
-          <t>Sir G.  Integrated Farm</t>
+          <t>On-call (private)</t>
         </is>
       </c>
       <c t="inlineStr" r="J30">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K30">
         <is>
-          <t>Organic Agriculture Production NC II</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L30">
         <is>
-          <t>CA-OAP0208642427009</t>
+          <t>CA-EIM0208642328016</t>
         </is>
       </c>
       <c t="inlineStr" r="M30">
         <is>
-          <t>2/28/2024</t>
+          <t>11/28/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N30">
         <is>
-          <t>2/10/2027</t>
+          <t>9/24/2028</t>
         </is>
       </c>
     </row>
@@ -2376,12 +2371,12 @@
       </c>
       <c t="inlineStr" r="C31">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Ranulfo Datoy Kuizon Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D31">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E31">
@@ -2391,7 +2386,7 @@
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t>4/7/1969</t>
+          <t>6/26/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
@@ -2401,32 +2396,37 @@
       </c>
       <c t="inlineStr" r="H31">
         <is>
-          <t>Competency Assessor</t>
+          <t>Trainer/assessor</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I31">
+        <is>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J31">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K31">
         <is>
-          <t>Animal Production (Poultry-Chicken) NC II</t>
+          <t>PV Systems Installation NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L31">
         <is>
-          <t>CA-APP0208642428018</t>
+          <t>CA-PVI0208642428012</t>
         </is>
       </c>
       <c t="inlineStr" r="M31">
         <is>
-          <t>4/16/2024</t>
+          <t>2/28/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N31">
         <is>
-          <t>12/6/2028</t>
+          <t>10/12/2028</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c t="inlineStr" r="C32">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Ranulfo Datoy Kuizon Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D32">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E32">
@@ -2458,7 +2458,7 @@
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t>4/7/1969</t>
+          <t>6/26/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
@@ -2468,37 +2468,37 @@
       </c>
       <c t="inlineStr" r="H32">
         <is>
-          <t>Accredited Competency Assessor</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I32">
         <is>
-          <t>On-call</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J32">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K32">
         <is>
-          <t>Agricultural Crops Production NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L32">
         <is>
-          <t>CA-ACP0208642428019</t>
+          <t>CA-EAW0108642428003</t>
         </is>
       </c>
       <c t="inlineStr" r="M32">
         <is>
-          <t>4/30/2024</t>
+          <t>1/5/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N32">
         <is>
-          <t>11/18/2028</t>
+          <t>11/15/2028</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c t="inlineStr" r="C33">
         <is>
-          <t>Michael Mostaza Diaz</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D33">
         <is>
-          <t>76 A. Luna Street  City of Baybay Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E33">
@@ -2530,47 +2530,47 @@
       </c>
       <c t="inlineStr" r="F33">
         <is>
-          <t>4/24/1985</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G33">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H33">
         <is>
-          <t>Competency Assessor</t>
+          <t>Accredited Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I33">
         <is>
-          <t>Freelancer</t>
+          <t>On-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J33">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K33">
         <is>
-          <t>Events Management Services NC III</t>
+          <t>Agricultural Crops Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L33">
         <is>
-          <t>CA-EVM0308642328010</t>
+          <t>CA-ACP0208642428019</t>
         </is>
       </c>
       <c t="inlineStr" r="M33">
         <is>
-          <t>6/30/2023</t>
+          <t>4/30/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N33">
         <is>
-          <t>4/16/2028</t>
+          <t>11/18/2028</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c t="inlineStr" r="C34">
         <is>
-          <t>Rico Bitor Ampo</t>
+          <t>Esmeraldo Palazon Orail Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D34">
         <is>
-          <t>Brgy. San Roque Sogod Southern Leyte</t>
+          <t>Mahayahay Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E34">
@@ -2602,47 +2602,47 @@
       </c>
       <c t="inlineStr" r="F34">
         <is>
-          <t>8/17/1961</t>
+          <t>10/6/1981</t>
         </is>
       </c>
       <c t="inlineStr" r="G34">
         <is>
-          <t>Masteral</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H34">
         <is>
-          <t>Associate Professor</t>
+          <t>Company Driver</t>
         </is>
       </c>
       <c t="inlineStr" r="I34">
         <is>
-          <t>Southern Leyte State University - Sogod Campus</t>
+          <t>Ghraze Jhoy Techncial Vocational School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J34">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K34">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Driving (Passenger Bus/Straight Truck) NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L34">
         <is>
-          <t>ELCEIM21502086424290001</t>
+          <t>ALTDRB31103086425280016</t>
         </is>
       </c>
       <c t="inlineStr" r="M34">
         <is>
-          <t>9/9/2024</t>
+          <t>8/29/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N34">
         <is>
-          <t>4/21/2029</t>
+          <t>12/3/2028</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c t="inlineStr" r="C35">
         <is>
-          <t>Roger . Ladica .</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D35">
         <is>
-          <t>Ponong Bato Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E35">
@@ -2674,7 +2674,7 @@
       </c>
       <c t="inlineStr" r="F35">
         <is>
-          <t>3/2/1976</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G35">
@@ -2684,37 +2684,32 @@
       </c>
       <c t="inlineStr" r="H35">
         <is>
-          <t>Trainer</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I35">
-        <is>
-          <t>Bato Institute Of Science And Technology</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="J35">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K35">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
+          <t>Animal Production (Poultry-Chicken) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L35">
         <is>
-          <t>MEEEAW20602086424290002</t>
+          <t>CA-APP0208642428018</t>
         </is>
       </c>
       <c t="inlineStr" r="M35">
         <is>
-          <t>9/9/2024</t>
+          <t>4/16/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N35">
         <is>
-          <t>6/17/2029</t>
+          <t>12/6/2028</t>
         </is>
       </c>
     </row>
@@ -2731,12 +2726,12 @@
       </c>
       <c t="inlineStr" r="C36">
         <is>
-          <t>Orlando Coquilla Paas Sr.</t>
+          <t>Ghubert Fedival Francisco</t>
         </is>
       </c>
       <c t="inlineStr" r="D36">
         <is>
-          <t>2-a New Ahayag Saint Bernard Southern Leyte</t>
+          <t>Brgy. 91 Abucay Tacloban City Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E36">
@@ -2746,47 +2741,47 @@
       </c>
       <c t="inlineStr" r="F36">
         <is>
-          <t>11/9/1973</t>
+          <t>6/28/1976</t>
         </is>
       </c>
       <c t="inlineStr" r="G36">
         <is>
-          <t>College Graduate</t>
+          <t>Doctorate</t>
         </is>
       </c>
       <c t="inlineStr" r="H36">
         <is>
-          <t>Electrician</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I36">
         <is>
-          <t>Southern Leyte Electric Cooperatie Incorporated</t>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J36">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Social, Community Development and Other Services</t>
         </is>
       </c>
       <c t="inlineStr" r="K36">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Bookkeeping NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L36">
         <is>
-          <t>ELCEIM21502086424290003</t>
+          <t>CA-BKP0308642428007</t>
         </is>
       </c>
       <c t="inlineStr" r="M36">
         <is>
-          <t>9/9/2024</t>
+          <t>2/26/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N36">
         <is>
-          <t>3/20/2029</t>
+          <t>12/21/2028</t>
         </is>
       </c>
     </row>
@@ -2803,22 +2798,22 @@
       </c>
       <c t="inlineStr" r="C37">
         <is>
-          <t>Mikhaela Ysabelle Laplana Caores</t>
+          <t>Kierzner Dounee Ordiz Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D37">
         <is>
-          <t>Brgy. Mambajo City of Maasin Southern Leyte</t>
+          <t>Mambajao City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E37">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F37">
         <is>
-          <t>11/11/1996</t>
+          <t>3/30/1996</t>
         </is>
       </c>
       <c t="inlineStr" r="G37">
@@ -2828,37 +2823,37 @@
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t>Job Order/ Bookkeeper</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I37">
         <is>
-          <t>Provincial Local Government Unit, Southern Leyte</t>
+          <t>On-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J37">
         <is>
-          <t>Social, Community Development and Other Services</t>
+          <t>Human Health / Health Care</t>
         </is>
       </c>
       <c t="inlineStr" r="K37">
         <is>
-          <t>Bookkeeping NC III</t>
+          <t>Health Care Services NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L37">
         <is>
-          <t>SOCBKP30703086424290004</t>
+          <t>CA-HCS0208642429001</t>
         </is>
       </c>
       <c t="inlineStr" r="M37">
         <is>
-          <t>9/16/2024</t>
+          <t>1/5/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N37">
         <is>
-          <t>5/28/2029</t>
+          <t>1/3/2029</t>
         </is>
       </c>
     </row>
@@ -2875,22 +2870,22 @@
       </c>
       <c t="inlineStr" r="C38">
         <is>
-          <t>Creliza F. Gamay</t>
+          <t>Rodolfo Paloma Flores</t>
         </is>
       </c>
       <c t="inlineStr" r="D38">
         <is>
-          <t>Brgy. Poblacion Las Navas Northern Samar</t>
+          <t>Baranggay Gakak,  Libagon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E38">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F38">
         <is>
-          <t>9/22/1974</t>
+          <t>3/2/1961</t>
         </is>
       </c>
       <c t="inlineStr" r="G38">
@@ -2900,37 +2895,37 @@
       </c>
       <c t="inlineStr" r="H38">
         <is>
-          <t>Sr. Tesd Specialist</t>
+          <t>Freelancer</t>
         </is>
       </c>
       <c t="inlineStr" r="I38">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>Freelancer</t>
         </is>
       </c>
       <c t="inlineStr" r="J38">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K38">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L38">
         <is>
-          <t>TRSBPP20902086424290005</t>
+          <t>ELCEIM21502086425290012</t>
         </is>
       </c>
       <c t="inlineStr" r="M38">
         <is>
-          <t>10/24/2024</t>
+          <t>8/22/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N38">
         <is>
-          <t>5/26/2029</t>
+          <t>2/21/2029</t>
         </is>
       </c>
     </row>
@@ -2947,37 +2942,37 @@
       </c>
       <c t="inlineStr" r="C39">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Maria Normida Ordiz Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D39">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>R. Kangleon Street Brgy. Mambajao,  City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E39">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F39">
         <is>
-          <t>10/13/1993</t>
+          <t>12/6/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G39">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H39">
         <is>
-          <t>Trainer</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I39">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J39">
@@ -2992,17 +2987,17 @@
       </c>
       <c t="inlineStr" r="L39">
         <is>
-          <t>TRSCOK21402086424290006</t>
+          <t>CA-COK0208642429006</t>
         </is>
       </c>
       <c t="inlineStr" r="M39">
         <is>
-          <t>10/24/2024</t>
+          <t>2/26/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N39">
         <is>
-          <t>6/2/2029</t>
+          <t>2/22/2029</t>
         </is>
       </c>
     </row>
@@ -3019,32 +3014,32 @@
       </c>
       <c t="inlineStr" r="C40">
         <is>
-          <t>Maria Normida Ordiz Caores</t>
+          <t>Harris Zabala Aguilando</t>
         </is>
       </c>
       <c t="inlineStr" r="D40">
         <is>
-          <t>R. Kangleon Street Brgy. Mambajao,  City of Maasin Southern Leyte</t>
+          <t>Las Navas Northern Samar</t>
         </is>
       </c>
       <c t="inlineStr" r="E40">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F40">
         <is>
-          <t>12/6/1969</t>
+          <t>8/23/1977</t>
         </is>
       </c>
       <c t="inlineStr" r="G40">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H40">
         <is>
-          <t>Tesd Specialist 2</t>
+          <t>Sr. Tesd Specialist</t>
         </is>
       </c>
       <c t="inlineStr" r="I40">
@@ -3054,27 +3049,27 @@
       </c>
       <c t="inlineStr" r="J40">
         <is>
-          <t>Social, Community Development and Other Services</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K40">
         <is>
-          <t>Bookkeeping NC III</t>
+          <t>Animal Production (Swine) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L40">
         <is>
-          <t>SOCBKP30703086424290007</t>
+          <t>AFFAPS21302086425290009</t>
         </is>
       </c>
       <c t="inlineStr" r="M40">
         <is>
-          <t>10/24/2024</t>
+          <t>8/22/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N40">
         <is>
-          <t>5/28/2029</t>
+          <t>2/26/2029</t>
         </is>
       </c>
     </row>
@@ -3091,12 +3086,12 @@
       </c>
       <c t="inlineStr" r="C41">
         <is>
-          <t>Marven Dejarme Estinozo</t>
+          <t>Orlando Coquilla Paas Sr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D41">
         <is>
-          <t>Brgy. Consolacion Sogod Southern Leyte</t>
+          <t>2-a New Ahayag Saint Bernard Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E41">
@@ -3106,7 +3101,7 @@
       </c>
       <c t="inlineStr" r="F41">
         <is>
-          <t>1/3/1983</t>
+          <t>11/9/1973</t>
         </is>
       </c>
       <c t="inlineStr" r="G41">
@@ -3116,12 +3111,12 @@
       </c>
       <c t="inlineStr" r="H41">
         <is>
-          <t>Head Computer Technician</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c t="inlineStr" r="I41">
         <is>
-          <t>Arc Tutorials Learning Services Inc.</t>
+          <t>Southern Leyte Electric Cooperatie Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="J41">
@@ -3131,22 +3126,22 @@
       </c>
       <c t="inlineStr" r="K41">
         <is>
-          <t>Computer Systems Servicing NC II</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L41">
         <is>
-          <t>ELCCSS21302086424280008</t>
+          <t>ELCEIM21502086424290003</t>
         </is>
       </c>
       <c t="inlineStr" r="M41">
         <is>
-          <t>10/24/2024</t>
+          <t>9/9/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N41">
         <is>
-          <t>5/18/2028</t>
+          <t>3/20/2029</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3158,12 @@
       </c>
       <c t="inlineStr" r="C42">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Rico Bitor Ampo</t>
         </is>
       </c>
       <c t="inlineStr" r="D42">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Brgy. San Roque Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E42">
@@ -3178,47 +3173,47 @@
       </c>
       <c t="inlineStr" r="F42">
         <is>
-          <t>4/7/1969</t>
+          <t>8/17/1961</t>
         </is>
       </c>
       <c t="inlineStr" r="G42">
         <is>
-          <t>College Undergraduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H42">
         <is>
-          <t>Farm Administrator</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c t="inlineStr" r="I42">
         <is>
-          <t>Marsia Flora Integrated Farm</t>
+          <t>Southern Leyte State University - Sogod Campus</t>
         </is>
       </c>
       <c t="inlineStr" r="J42">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K42">
         <is>
-          <t>Agroentrepreneurship NC II</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L42">
         <is>
-          <t>AFFAGE21702086425290001</t>
+          <t>ELCEIM21502086424290001</t>
         </is>
       </c>
       <c t="inlineStr" r="M42">
         <is>
-          <t>1/15/2025</t>
+          <t>9/9/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N42">
         <is>
-          <t>7/1/2029</t>
+          <t>4/21/2029</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3230,12 @@
       </c>
       <c t="inlineStr" r="C43">
         <is>
-          <t>Eduardo Lora Bosque</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D43">
         <is>
-          <t>San Rafael City of Maasin Southern Leyte</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E43">
@@ -3250,47 +3245,47 @@
       </c>
       <c t="inlineStr" r="F43">
         <is>
-          <t>3/27/1987</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G43">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t>Head Mechanic</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I43">
         <is>
-          <t>Phil - Auto Citi Services Inc.</t>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J43">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K43">
         <is>
-          <t>Driving NC II</t>
+          <t>Agricultural Crops Production NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L43">
         <is>
-          <t>ALTDRV20402086425300002</t>
+          <t>AFFACP30603086426290005</t>
         </is>
       </c>
       <c t="inlineStr" r="M43">
         <is>
-          <t>5/27/2025</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N43">
         <is>
-          <t>1/21/2030</t>
+          <t>5/2/2029</t>
         </is>
       </c>
     </row>
@@ -3307,22 +3302,22 @@
       </c>
       <c t="inlineStr" r="C44">
         <is>
-          <t>Ma. Asuncion Bagolor Mendoza</t>
+          <t>Eduardo Lora Bosque</t>
         </is>
       </c>
       <c t="inlineStr" r="D44">
         <is>
-          <t>Brgy. Dongon City of Maasin Southern Leyte</t>
+          <t>San Rafael City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E44">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F44">
         <is>
-          <t>8/10/1979</t>
+          <t>3/27/1987</t>
         </is>
       </c>
       <c t="inlineStr" r="G44">
@@ -3332,37 +3327,37 @@
       </c>
       <c t="inlineStr" r="H44">
         <is>
-          <t>Senior High School Teacher And College Teacher</t>
+          <t>Head Mechanic</t>
         </is>
       </c>
       <c t="inlineStr" r="I44">
         <is>
-          <t>The College Of Maasin, Inc.</t>
+          <t>Phil Auto Citi Services Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="J44">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K44">
         <is>
-          <t>Cookery NC II</t>
+          <t>Automotive Servicing NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L44">
         <is>
-          <t>TRSCOK21402086425290003</t>
+          <t>ALTATS11801086426290021</t>
         </is>
       </c>
       <c t="inlineStr" r="M44">
         <is>
-          <t>5/27/2025</t>
+          <t>6/25/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N44">
         <is>
-          <t>9/16/2029</t>
+          <t>5/15/2029</t>
         </is>
       </c>
     </row>
@@ -3419,22 +3414,22 @@
       </c>
       <c t="inlineStr" r="K45">
         <is>
-          <t>Cookery NC II</t>
+          <t>Bread and Pastry Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L45">
         <is>
-          <t>TRSCOK21402086425290004</t>
+          <t>TRSBPP20902086424290005</t>
         </is>
       </c>
       <c t="inlineStr" r="M45">
         <is>
-          <t>6/18/2025</t>
+          <t>10/24/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N45">
         <is>
-          <t>11/4/2029</t>
+          <t>5/26/2029</t>
         </is>
       </c>
     </row>
@@ -3451,62 +3446,62 @@
       </c>
       <c t="inlineStr" r="C46">
         <is>
-          <t>Cerecio Cabudbud Mendoza</t>
+          <t>Mikhaela Ysabelle Laplana Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D46">
         <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
+          <t>Brgy. Mambajo City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E46">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F46">
         <is>
-          <t>2/21/1960</t>
+          <t>11/11/1996</t>
         </is>
       </c>
       <c t="inlineStr" r="G46">
         <is>
-          <t>Masteral</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H46">
         <is>
-          <t>Head Teacher Iii</t>
+          <t>Job Order/ Bookkeeper</t>
         </is>
       </c>
       <c t="inlineStr" r="I46">
         <is>
-          <t>Villa Jacinta National Vocational High School</t>
+          <t>Provincial Local Government Unit, Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J46">
         <is>
-          <t>Construction</t>
+          <t>Social, Community Development and Other Services</t>
         </is>
       </c>
       <c t="inlineStr" r="K46">
         <is>
-          <t>Carpentry NC II</t>
+          <t>Bookkeeping NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L46">
         <is>
-          <t>CONCAR21802086425300005</t>
+          <t>SOCBKP30703086424290004</t>
         </is>
       </c>
       <c t="inlineStr" r="M46">
         <is>
-          <t>6/18/2025</t>
+          <t>9/16/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N46">
         <is>
-          <t>1/27/2030</t>
+          <t>5/28/2029</t>
         </is>
       </c>
     </row>
@@ -3523,62 +3518,62 @@
       </c>
       <c t="inlineStr" r="C47">
         <is>
-          <t>Cerecio Cabudbud Mendoza</t>
+          <t>Maria Normida Ordiz Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D47">
         <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
+          <t>R. Kangleon Street Brgy. Mambajao,  City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E47">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F47">
         <is>
-          <t>2/21/1960</t>
+          <t>12/6/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G47">
         <is>
-          <t>Masteral</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H47">
         <is>
-          <t>Head Teacher Iii</t>
+          <t>Tesd Specialist 2</t>
         </is>
       </c>
       <c t="inlineStr" r="I47">
         <is>
-          <t>Villa Jacinta Nationalvocational High School</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J47">
         <is>
-          <t>Construction</t>
+          <t>Social, Community Development and Other Services</t>
         </is>
       </c>
       <c t="inlineStr" r="K47">
         <is>
-          <t>Masonry NC II</t>
+          <t>Bookkeeping NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L47">
         <is>
-          <t>CONMAS21802086425300006</t>
+          <t>SOCBKP30703086424290007</t>
         </is>
       </c>
       <c t="inlineStr" r="M47">
         <is>
-          <t>6/18/2025</t>
+          <t>10/24/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N47">
         <is>
-          <t>1/27/2030</t>
+          <t>5/28/2029</t>
         </is>
       </c>
     </row>
@@ -3595,12 +3590,12 @@
       </c>
       <c t="inlineStr" r="C48">
         <is>
-          <t>Cerecio Cabudbud Mendoza</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D48">
         <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E48">
@@ -3610,47 +3605,47 @@
       </c>
       <c t="inlineStr" r="F48">
         <is>
-          <t>2/21/1960</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G48">
         <is>
-          <t>Masteral</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H48">
         <is>
-          <t>Head Teacher Iii</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I48">
         <is>
-          <t>Villa Jacinta National Vocational High School</t>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J48">
         <is>
-          <t>Construction</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K48">
         <is>
-          <t>Tile Setting NC II</t>
+          <t>Cookery NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L48">
         <is>
-          <t>CONTIL21802086425290007</t>
+          <t>TRSCOK21402086424290006</t>
         </is>
       </c>
       <c t="inlineStr" r="M48">
         <is>
-          <t>6/18/2025</t>
+          <t>10/24/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N48">
         <is>
-          <t>11/13/2029</t>
+          <t>6/2/2029</t>
         </is>
       </c>
     </row>
@@ -3667,62 +3662,62 @@
       </c>
       <c t="inlineStr" r="C49">
         <is>
-          <t>Shiela Bernaldez Diangco</t>
+          <t>Roger . Ladica .</t>
         </is>
       </c>
       <c t="inlineStr" r="D49">
         <is>
-          <t>Poblacion, Liloan Southern Leyte</t>
+          <t>Ponong Bato Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E49">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F49">
         <is>
-          <t>6/16/1970</t>
+          <t>3/2/1976</t>
         </is>
       </c>
       <c t="inlineStr" r="G49">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H49">
         <is>
-          <t>Teacher 2</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I49">
         <is>
-          <t>Liloan National Technical Vocational High School</t>
+          <t>Bato Institute Of Science And Technology</t>
         </is>
       </c>
       <c t="inlineStr" r="J49">
         <is>
-          <t>Garments</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K49">
         <is>
-          <t>Dressmaking NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L49">
         <is>
-          <t>GRMDRM20502086425290008</t>
+          <t>MEEEAW20602086424290002</t>
         </is>
       </c>
       <c t="inlineStr" r="M49">
         <is>
-          <t>8/22/2025</t>
+          <t>9/9/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N49">
         <is>
-          <t>7/9/2029</t>
+          <t>6/17/2029</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3734,12 @@
       </c>
       <c t="inlineStr" r="C50">
         <is>
-          <t>Harris Zabala Aguilando</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D50">
         <is>
-          <t>Las Navas Northern Samar</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E50">
@@ -3754,22 +3749,22 @@
       </c>
       <c t="inlineStr" r="F50">
         <is>
-          <t>8/23/1977</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G50">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t>Sr. Tesd Specialist</t>
+          <t>Farm Administrator</t>
         </is>
       </c>
       <c t="inlineStr" r="I50">
         <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
+          <t>Marsia Flora Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J50">
@@ -3779,22 +3774,22 @@
       </c>
       <c t="inlineStr" r="K50">
         <is>
-          <t>Animal Production (Swine) NC II</t>
+          <t>Agroentrepreneurship NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L50">
         <is>
-          <t>AFFAPS21302086425290009</t>
+          <t>AFFAGE21702086425290001</t>
         </is>
       </c>
       <c t="inlineStr" r="M50">
         <is>
-          <t>8/22/2025</t>
+          <t>1/15/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N50">
         <is>
-          <t>2/26/2029</t>
+          <t>7/1/2029</t>
         </is>
       </c>
     </row>
@@ -3811,22 +3806,22 @@
       </c>
       <c t="inlineStr" r="C51">
         <is>
-          <t>Harris Zabala Aguilando</t>
+          <t>Shiela Bernaldez Diangco</t>
         </is>
       </c>
       <c t="inlineStr" r="D51">
         <is>
-          <t>Las Navas Northern Samar</t>
+          <t>Poblacion, Liloan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E51">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F51">
         <is>
-          <t>8/23/1977</t>
+          <t>6/16/1970</t>
         </is>
       </c>
       <c t="inlineStr" r="G51">
@@ -3836,27 +3831,27 @@
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t>Sr. Tesd Specialist</t>
+          <t>Teacher 2</t>
         </is>
       </c>
       <c t="inlineStr" r="I51">
         <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
+          <t>Liloan National Technical Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J51">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Garments</t>
         </is>
       </c>
       <c t="inlineStr" r="K51">
         <is>
-          <t>Animal Production (Ruminants) NC II</t>
+          <t>Dressmaking NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L51">
         <is>
-          <t>AFFAPR21302086425260010</t>
+          <t>GRMDRM20502086425290008</t>
         </is>
       </c>
       <c t="inlineStr" r="M51">
@@ -3866,7 +3861,7 @@
       </c>
       <c t="inlineStr" r="N51">
         <is>
-          <t>11/30/2026</t>
+          <t>7/9/2029</t>
         </is>
       </c>
     </row>
@@ -3883,22 +3878,22 @@
       </c>
       <c t="inlineStr" r="C52">
         <is>
-          <t>Marie Fe Matunog Adan</t>
+          <t>Rhett Togonon Binghoy</t>
         </is>
       </c>
       <c t="inlineStr" r="D52">
         <is>
-          <t>Purok B Bangcas A Hinunangan Southern Leyte</t>
+          <t>Salog Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E52">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F52">
         <is>
-          <t>5/26/1989</t>
+          <t>2/24/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G52">
@@ -3908,37 +3903,37 @@
       </c>
       <c t="inlineStr" r="H52">
         <is>
-          <t>Trainer/ Admin Support Staff</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I52">
         <is>
-          <t>Ssm Integrated Farm</t>
+          <t>Pacific Vocational Training Center Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J52">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K52">
         <is>
-          <t>Organic Agriculture Production NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L52">
         <is>
-          <t>AFFOAP21202086425300011</t>
+          <t>MEEEAW10601086426290016</t>
         </is>
       </c>
       <c t="inlineStr" r="M52">
         <is>
-          <t>8/22/2025</t>
+          <t>6/8/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N52">
         <is>
-          <t>3/3/2030</t>
+          <t>7/24/2029</t>
         </is>
       </c>
     </row>
@@ -3955,12 +3950,12 @@
       </c>
       <c t="inlineStr" r="C53">
         <is>
-          <t>Rodolfo Paloma Flores</t>
+          <t>Allen Dolorito Monter</t>
         </is>
       </c>
       <c t="inlineStr" r="D53">
         <is>
-          <t>Baranggay Gakak,  Libagon Southern Leyte</t>
+          <t>Asuncion City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E53">
@@ -3970,12 +3965,12 @@
       </c>
       <c t="inlineStr" r="F53">
         <is>
-          <t>3/2/1961</t>
+          <t>9/18/1990</t>
         </is>
       </c>
       <c t="inlineStr" r="G53">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H53">
@@ -3990,27 +3985,27 @@
       </c>
       <c t="inlineStr" r="J53">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K53">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L53">
         <is>
-          <t>ELCEIM21502086425290012</t>
+          <t>MEEEAW10601086425290015</t>
         </is>
       </c>
       <c t="inlineStr" r="M53">
         <is>
-          <t>8/22/2025</t>
+          <t>8/29/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N53">
         <is>
-          <t>2/21/2029</t>
+          <t>9/15/2029</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4022,22 @@
       </c>
       <c t="inlineStr" r="C54">
         <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
+          <t>Ma. Asuncion Bagolor Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D54">
         <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
+          <t>Brgy. Dongon City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E54">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F54">
         <is>
-          <t>6/26/1983</t>
+          <t>8/10/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G54">
@@ -4052,37 +4047,37 @@
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t>Administrative Assistant Iii</t>
+          <t>Senior High School Teacher And College Teacher</t>
         </is>
       </c>
       <c t="inlineStr" r="I54">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>The College Of Maasin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J54">
         <is>
-          <t>Construction</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K54">
         <is>
-          <t>Heavy Equipment Operation (Hydraulic Excavator) NC II</t>
+          <t>Cookery NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L54">
         <is>
-          <t>CONHEO21902086425260013</t>
+          <t>TRSCOK21402086425290003</t>
         </is>
       </c>
       <c t="inlineStr" r="M54">
         <is>
-          <t>8/29/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N54">
         <is>
-          <t>10/1/2026</t>
+          <t>9/16/2029</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4094,12 @@
       </c>
       <c t="inlineStr" r="C55">
         <is>
-          <t>Ma. Luisa Garong Terre</t>
+          <t>Lucia Misal Villarias</t>
         </is>
       </c>
       <c t="inlineStr" r="D55">
         <is>
-          <t>Ibarra City of Maasin Southern Leyte</t>
+          <t>Zone 1 Mangkaw Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E55">
@@ -4114,7 +4109,7 @@
       </c>
       <c t="inlineStr" r="F55">
         <is>
-          <t>5/18/1976</t>
+          <t>12/13/1959</t>
         </is>
       </c>
       <c t="inlineStr" r="G55">
@@ -4124,37 +4119,37 @@
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t>C Omputer Iinstructor/ Processor</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I55">
         <is>
-          <t>St. Thiomas Aquimas College</t>
+          <t>Ghrace Jhoy Technical And Vocational School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J55">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K55">
         <is>
-          <t>Computer Systems Servicing NC II</t>
+          <t>Cookery NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L55">
         <is>
-          <t>ELCCSS21302086425300014</t>
+          <t>TRSCOK21402086426290019</t>
         </is>
       </c>
       <c t="inlineStr" r="M55">
         <is>
-          <t>8/29/2025</t>
+          <t>6/8/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N55">
         <is>
-          <t>4/20/2030</t>
+          <t>10/20/2029</t>
         </is>
       </c>
     </row>
@@ -4171,62 +4166,62 @@
       </c>
       <c t="inlineStr" r="C56">
         <is>
-          <t>Allen Dolorito Monter</t>
+          <t>Creliza F. Gamay</t>
         </is>
       </c>
       <c t="inlineStr" r="D56">
         <is>
-          <t>Asuncion City of Maasin Southern Leyte</t>
+          <t>Brgy. Poblacion Las Navas Northern Samar</t>
         </is>
       </c>
       <c t="inlineStr" r="E56">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F56">
         <is>
-          <t>9/18/1990</t>
+          <t>9/22/1974</t>
         </is>
       </c>
       <c t="inlineStr" r="G56">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H56">
         <is>
-          <t>Freelancer</t>
+          <t>Sr. Tesd Specialist</t>
         </is>
       </c>
       <c t="inlineStr" r="I56">
         <is>
-          <t>Freelancer</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J56">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K56">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Cookery NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L56">
         <is>
-          <t>MEEEAW10601086425290015</t>
+          <t>TRSCOK21402086425290004</t>
         </is>
       </c>
       <c t="inlineStr" r="M56">
         <is>
-          <t>8/29/2025</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N56">
         <is>
-          <t>9/15/2029</t>
+          <t>11/4/2029</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4238,12 @@
       </c>
       <c t="inlineStr" r="C57">
         <is>
-          <t>Esmeraldo Palazon Orail Jr.</t>
+          <t>Cerecio Cabudbud Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D57">
         <is>
-          <t>Mahayahay Sogod Southern Leyte</t>
+          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E57">
@@ -4258,47 +4253,47 @@
       </c>
       <c t="inlineStr" r="F57">
         <is>
-          <t>10/6/1981</t>
+          <t>2/21/1960</t>
         </is>
       </c>
       <c t="inlineStr" r="G57">
         <is>
-          <t>College Graduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H57">
         <is>
-          <t>Company Driver</t>
+          <t>Head Teacher Iii</t>
         </is>
       </c>
       <c t="inlineStr" r="I57">
         <is>
-          <t>Ghraze Jhoy Techncial Vocational School Inc.</t>
+          <t>Villa Jacinta National Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J57">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K57">
         <is>
-          <t>Driving (Passenger Bus/Straight Truck) NC III</t>
+          <t>Tile Setting NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L57">
         <is>
-          <t>ALTDRB31103086425280016</t>
+          <t>CONTIL21802086425290007</t>
         </is>
       </c>
       <c t="inlineStr" r="M57">
         <is>
-          <t>8/29/2025</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N57">
         <is>
-          <t>12/3/2028</t>
+          <t>11/13/2029</t>
         </is>
       </c>
     </row>
@@ -4315,12 +4310,12 @@
       </c>
       <c t="inlineStr" r="C58">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Eduardo Lora Bosque</t>
         </is>
       </c>
       <c t="inlineStr" r="D58">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>San Rafael City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E58">
@@ -4330,37 +4325,47 @@
       </c>
       <c t="inlineStr" r="F58">
         <is>
-          <t>10/13/1993</t>
+          <t>3/27/1987</t>
         </is>
       </c>
       <c t="inlineStr" r="G58">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H58">
+        <is>
+          <t>Head Mechanic</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I58">
+        <is>
+          <t>Phil - Auto Citi Services Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J58">
         <is>
-          <t>TVET</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K58">
         <is>
-          <t>Trainers Methodology Level  NC I</t>
+          <t>Driving NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L58">
         <is>
-          <t>TVETRM11101000025260282</t>
+          <t>ALTDRV20402086425300002</t>
         </is>
       </c>
       <c t="inlineStr" r="M58">
         <is>
-          <t>12/6/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N58">
         <is>
-          <t>12/5/2026</t>
+          <t>1/21/2030</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4382,12 @@
       </c>
       <c t="inlineStr" r="C59">
         <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
+          <t>Cerecio Cabudbud Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D59">
         <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
+          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E59">
@@ -4392,22 +4397,22 @@
       </c>
       <c t="inlineStr" r="F59">
         <is>
-          <t>6/26/1983</t>
+          <t>2/21/1960</t>
         </is>
       </c>
       <c t="inlineStr" r="G59">
         <is>
-          <t>College Undergraduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H59">
         <is>
-          <t>Administrative Assistant 3</t>
+          <t>Head Teacher Iii</t>
         </is>
       </c>
       <c t="inlineStr" r="I59">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>Villa Jacinta National Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J59">
@@ -4417,22 +4422,22 @@
       </c>
       <c t="inlineStr" r="K59">
         <is>
-          <t>Tile Setting NC II</t>
+          <t>Carpentry NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L59">
         <is>
-          <t>CONTIL21802086426300001</t>
+          <t>CONCAR21802086425300005</t>
         </is>
       </c>
       <c t="inlineStr" r="M59">
         <is>
-          <t>1/23/2026</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N59">
         <is>
-          <t>10/14/2030</t>
+          <t>1/27/2030</t>
         </is>
       </c>
     </row>
@@ -4449,12 +4454,12 @@
       </c>
       <c t="inlineStr" r="C60">
         <is>
-          <t>Amiel Lora Bosque</t>
+          <t>Cerecio Cabudbud Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D60">
         <is>
-          <t>Brgy. San Rafael City of Maasin Southern Leyte</t>
+          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E60">
@@ -4464,47 +4469,47 @@
       </c>
       <c t="inlineStr" r="F60">
         <is>
-          <t>10/11/1983</t>
+          <t>2/21/1960</t>
         </is>
       </c>
       <c t="inlineStr" r="G60">
         <is>
-          <t>College Undergraduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H60">
         <is>
-          <t>Welder</t>
+          <t>Head Teacher Iii</t>
         </is>
       </c>
       <c t="inlineStr" r="I60">
         <is>
-          <t>Ac Marine Services</t>
+          <t>Villa Jacinta Nationalvocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J60">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K60">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
+          <t>Masonry NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L60">
         <is>
-          <t>MEEEAW20602086426300002</t>
+          <t>CONMAS21802086425300006</t>
         </is>
       </c>
       <c t="inlineStr" r="M60">
         <is>
-          <t>1/23/2026</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N60">
         <is>
-          <t>8/28/2030</t>
+          <t>1/27/2030</t>
         </is>
       </c>
     </row>
@@ -4521,22 +4526,22 @@
       </c>
       <c t="inlineStr" r="C61">
         <is>
-          <t>Jordan Morata Catubig</t>
+          <t>Marie Fe Matunog Adan</t>
         </is>
       </c>
       <c t="inlineStr" r="D61">
         <is>
-          <t>M. H. Del Pilar Taliwa Malitbog Southern Leyte</t>
+          <t>Purok B Bangcas A Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E61">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F61">
         <is>
-          <t>9/8/1977</t>
+          <t>5/26/1989</t>
         </is>
       </c>
       <c t="inlineStr" r="G61">
@@ -4546,37 +4551,37 @@
       </c>
       <c t="inlineStr" r="H61">
         <is>
-          <t>Electricain</t>
+          <t>Trainer/ Admin Support Staff</t>
         </is>
       </c>
       <c t="inlineStr" r="I61">
         <is>
-          <t>Southern Leyte Electric Cooperative, Inc.</t>
+          <t>Ssm Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J61">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K61">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Organic Agriculture Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L61">
         <is>
-          <t>ELCEIM21502086426300003</t>
+          <t>AFFOAP21202086425300011</t>
         </is>
       </c>
       <c t="inlineStr" r="M61">
         <is>
-          <t>1/23/2026</t>
+          <t>8/22/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N61">
         <is>
-          <t>3/5/2030</t>
+          <t>3/3/2030</t>
         </is>
       </c>
     </row>
@@ -4593,22 +4598,22 @@
       </c>
       <c t="inlineStr" r="C62">
         <is>
-          <t>Michel Tingcoy Pata</t>
+          <t>Jordan Morata Catubig</t>
         </is>
       </c>
       <c t="inlineStr" r="D62">
         <is>
-          <t>Mahayahay Bontoc Southern Leyte</t>
+          <t>M. H. Del Pilar Taliwa Malitbog Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E62">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F62">
         <is>
-          <t>8/24/1980</t>
+          <t>9/8/1977</t>
         </is>
       </c>
       <c t="inlineStr" r="G62">
@@ -4618,27 +4623,27 @@
       </c>
       <c t="inlineStr" r="H62">
         <is>
-          <t>Teacher 3</t>
+          <t>Electricain</t>
         </is>
       </c>
       <c t="inlineStr" r="I62">
         <is>
-          <t>Villa Jacinta National Vocational High School</t>
+          <t>Southern Leyte Electric Cooperative, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J62">
         <is>
-          <t>Garments</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K62">
         <is>
-          <t>Dressmaking NC II</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L62">
         <is>
-          <t>GRMDRM20502086426270004</t>
+          <t>ELCEIM21502086426300003</t>
         </is>
       </c>
       <c t="inlineStr" r="M62">
@@ -4648,7 +4653,7 @@
       </c>
       <c t="inlineStr" r="N62">
         <is>
-          <t>5/3/2027</t>
+          <t>3/5/2030</t>
         </is>
       </c>
     </row>
@@ -4665,22 +4670,22 @@
       </c>
       <c t="inlineStr" r="C63">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Ma. Luisa Garong Terre</t>
         </is>
       </c>
       <c t="inlineStr" r="D63">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>Ibarra City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E63">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F63">
         <is>
-          <t>10/13/1993</t>
+          <t>5/18/1976</t>
         </is>
       </c>
       <c t="inlineStr" r="G63">
@@ -4690,37 +4695,37 @@
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t>Trainer</t>
+          <t>C Omputer Iinstructor/ Processor</t>
         </is>
       </c>
       <c t="inlineStr" r="I63">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
+          <t>St. Thiomas Aquimas College</t>
         </is>
       </c>
       <c t="inlineStr" r="J63">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K63">
         <is>
-          <t>Agricultural Crops Production NC III</t>
+          <t>Computer Systems Servicing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L63">
         <is>
-          <t>AFFACP30603086426290005</t>
+          <t>ELCCSS21302086425300014</t>
         </is>
       </c>
       <c t="inlineStr" r="M63">
         <is>
-          <t>1/23/2026</t>
+          <t>8/29/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N63">
         <is>
-          <t>5/2/2029</t>
+          <t>4/20/2030</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4742,12 @@
       </c>
       <c t="inlineStr" r="C64">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Amiel Lora Bosque</t>
         </is>
       </c>
       <c t="inlineStr" r="D64">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>Brgy. San Rafael City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E64">
@@ -4752,47 +4757,47 @@
       </c>
       <c t="inlineStr" r="F64">
         <is>
-          <t>10/13/1993</t>
+          <t>10/11/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G64">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H64">
         <is>
-          <t>Head Trainer</t>
+          <t>Welder</t>
         </is>
       </c>
       <c t="inlineStr" r="I64">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
+          <t>Ac Marine Services</t>
         </is>
       </c>
       <c t="inlineStr" r="J64">
         <is>
-          <t>Construction</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K64">
         <is>
-          <t>Masonry NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L64">
         <is>
-          <t>CONMAS21802086426300006</t>
+          <t>MEEEAW20602086426300002</t>
         </is>
       </c>
       <c t="inlineStr" r="M64">
         <is>
-          <t>2/20/2026</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N64">
         <is>
-          <t>10/9/2030</t>
+          <t>8/28/2030</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4814,12 @@
       </c>
       <c t="inlineStr" r="C65">
         <is>
-          <t>Joel Piso Paler</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D65">
         <is>
-          <t>Hitawos Bontoc Southern Leyte</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E65">
@@ -4824,37 +4829,37 @@
       </c>
       <c t="inlineStr" r="F65">
         <is>
-          <t>4/18/2001</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G65">
         <is>
-          <t>Post Secondary Non-Tertiary/Technical Vocational Course Graduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H65">
         <is>
-          <t>Instructor</t>
+          <t>Head Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I65">
         <is>
-          <t>Farmfinity Resort</t>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J65">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K65">
         <is>
-          <t>Food and Beverage Services NC II</t>
+          <t>Masonry NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L65">
         <is>
-          <t>TRSFBS21302086426310008</t>
+          <t>CONMAS21802086426300006</t>
         </is>
       </c>
       <c t="inlineStr" r="M65">
@@ -4864,7 +4869,7 @@
       </c>
       <c t="inlineStr" r="N65">
         <is>
-          <t>2/18/2031</t>
+          <t>10/9/2030</t>
         </is>
       </c>
     </row>
@@ -4881,12 +4886,12 @@
       </c>
       <c t="inlineStr" r="C66">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Ranulfo Datoy Kuizon Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D66">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E66">
@@ -4896,7 +4901,7 @@
       </c>
       <c t="inlineStr" r="F66">
         <is>
-          <t>4/7/1969</t>
+          <t>6/26/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G66">
@@ -4906,37 +4911,37 @@
       </c>
       <c t="inlineStr" r="H66">
         <is>
-          <t>School Administrator</t>
+          <t>Administrative Assistant 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I66">
         <is>
-          <t>Marsia Fiona Agro - Industrial School Inc.</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J66">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K66">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Tile Setting NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L66">
         <is>
-          <t>TRSBPP20902086426310009</t>
+          <t>CONTIL21802086426300001</t>
         </is>
       </c>
       <c t="inlineStr" r="M66">
         <is>
-          <t>2/20/2026</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N66">
         <is>
-          <t>2/18/2031</t>
+          <t>10/14/2030</t>
         </is>
       </c>
     </row>
@@ -4953,22 +4958,22 @@
       </c>
       <c t="inlineStr" r="C67">
         <is>
-          <t>Carmelyn Oppus Liberato</t>
+          <t>Joedee Mark . Rodriguez</t>
         </is>
       </c>
       <c t="inlineStr" r="D67">
         <is>
-          <t>Brgy. Maanyag  Tomas Oppus Southern Leyte</t>
+          <t>Brgy. San Jose Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E67">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F67">
         <is>
-          <t>1/8/1998</t>
+          <t>1/20/1995</t>
         </is>
       </c>
       <c t="inlineStr" r="G67">
@@ -4978,37 +4983,37 @@
       </c>
       <c t="inlineStr" r="H67">
         <is>
-          <t>Trainer</t>
+          <t>Ac Manager</t>
         </is>
       </c>
       <c t="inlineStr" r="I67">
         <is>
-          <t>Ghrace Joy Technical And Vocational School Inc.</t>
+          <t>Southern Leyte Stete University</t>
         </is>
       </c>
       <c t="inlineStr" r="J67">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K67">
         <is>
-          <t>Food and Beverage Services NC II</t>
+          <t>Computer Systems Servicing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L67">
         <is>
-          <t>TRSFBS21302086426280010</t>
+          <t>ELCCSS21302086426300022</t>
         </is>
       </c>
       <c t="inlineStr" r="M67">
         <is>
-          <t>2/20/2026</t>
+          <t>6/25/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N67">
         <is>
-          <t>6/28/2028</t>
+          <t>10/22/2030</t>
         </is>
       </c>
     </row>
@@ -5025,12 +5030,12 @@
       </c>
       <c t="inlineStr" r="C68">
         <is>
-          <t>Brenda Napuli Balogo</t>
+          <t>Michel Tingcoy Pata</t>
         </is>
       </c>
       <c t="inlineStr" r="D68">
         <is>
-          <t>R. Garces Street Brgy. Tunga-tunga City of Maasin Southern Leyte</t>
+          <t>Mahayahay Bontoc Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E68">
@@ -5040,7 +5045,7 @@
       </c>
       <c t="inlineStr" r="F68">
         <is>
-          <t>5/23/1958</t>
+          <t>8/24/1980</t>
         </is>
       </c>
       <c t="inlineStr" r="G68">
@@ -5055,7 +5060,7 @@
       </c>
       <c t="inlineStr" r="I68">
         <is>
-          <t>Villa Jacinta National Vocational High School</t>
+          <t>Villa Jacinta Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J68">
@@ -5070,7 +5075,7 @@
       </c>
       <c t="inlineStr" r="L68">
         <is>
-          <t>TRSBPP20902086426310011</t>
+          <t>TRSBPP20902086426300014</t>
         </is>
       </c>
       <c t="inlineStr" r="M68">
@@ -5080,7 +5085,7 @@
       </c>
       <c t="inlineStr" r="N68">
         <is>
-          <t>1/12/2031</t>
+          <t>12/3/2030</t>
         </is>
       </c>
     </row>
@@ -5097,12 +5102,12 @@
       </c>
       <c t="inlineStr" r="C69">
         <is>
-          <t>Archiel Sacurom  Amora</t>
+          <t>Lucia Misal Villarias</t>
         </is>
       </c>
       <c t="inlineStr" r="D69">
         <is>
-          <t>Consolacion Sogod Southern Leyte</t>
+          <t>Zone 1 Mangkaw Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E69">
@@ -5112,7 +5117,7 @@
       </c>
       <c t="inlineStr" r="F69">
         <is>
-          <t>11/9/1996</t>
+          <t>12/13/1959</t>
         </is>
       </c>
       <c t="inlineStr" r="G69">
@@ -5122,27 +5127,27 @@
       </c>
       <c t="inlineStr" r="H69">
         <is>
-          <t>Trainer/ Registrar</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I69">
         <is>
-          <t>Arc Tutorial Learning Services Inc.</t>
+          <t>Ghrace Jhoy Technical Educational School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J69">
         <is>
-          <t>Social, Community Development and Other Services</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K69">
         <is>
-          <t>Early Childhood Care and Development Services NC III</t>
+          <t>Food and Beverage Services NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L69">
         <is>
-          <t>SOCECD32503086426300012</t>
+          <t>TRSFBS21302086426300013</t>
         </is>
       </c>
       <c t="inlineStr" r="M69">
@@ -5152,7 +5157,7 @@
       </c>
       <c t="inlineStr" r="N69">
         <is>
-          <t>12/14/2030</t>
+          <t>12/4/2030</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5204,7 @@
       </c>
       <c t="inlineStr" r="I70">
         <is>
-          <t>Ghrace Jhoy Technical Educational School Inc.</t>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J70">
@@ -5209,17 +5214,17 @@
       </c>
       <c t="inlineStr" r="K70">
         <is>
-          <t>Food and Beverage Services NC II</t>
+          <t>Housekeeping NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L70">
         <is>
-          <t>TRSFBS21302086426300013</t>
+          <t>TRSHSK21302086426300023</t>
         </is>
       </c>
       <c t="inlineStr" r="M70">
         <is>
-          <t>5/11/2026</t>
+          <t>9/2/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N70">
@@ -5241,12 +5246,12 @@
       </c>
       <c t="inlineStr" r="C71">
         <is>
-          <t>Michel Tingcoy Pata</t>
+          <t>Archiel Sacurom  Amora</t>
         </is>
       </c>
       <c t="inlineStr" r="D71">
         <is>
-          <t>Mahayahay Bontoc Southern Leyte</t>
+          <t>Consolacion Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E71">
@@ -5256,7 +5261,7 @@
       </c>
       <c t="inlineStr" r="F71">
         <is>
-          <t>8/24/1980</t>
+          <t>11/9/1996</t>
         </is>
       </c>
       <c t="inlineStr" r="G71">
@@ -5266,27 +5271,27 @@
       </c>
       <c t="inlineStr" r="H71">
         <is>
-          <t>Teacher 3</t>
+          <t>Trainer/ Registrar</t>
         </is>
       </c>
       <c t="inlineStr" r="I71">
         <is>
-          <t>Villa Jacinta Vocational High School</t>
+          <t>Arc Tutorial Learning Services Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J71">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Social, Community Development and Other Services</t>
         </is>
       </c>
       <c t="inlineStr" r="K71">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Early Childhood Care and Development Services NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L71">
         <is>
-          <t>TRSBPP20902086426300014</t>
+          <t>SOCECD32503086426300012</t>
         </is>
       </c>
       <c t="inlineStr" r="M71">
@@ -5296,7 +5301,7 @@
       </c>
       <c t="inlineStr" r="N71">
         <is>
-          <t>12/3/2030</t>
+          <t>12/14/2030</t>
         </is>
       </c>
     </row>
@@ -5313,22 +5318,22 @@
       </c>
       <c t="inlineStr" r="C72">
         <is>
-          <t>Rhett Togonon Binghoy</t>
+          <t>Brenda Napuli Balogo</t>
         </is>
       </c>
       <c t="inlineStr" r="D72">
         <is>
-          <t>Salog Hinunangan Southern Leyte</t>
+          <t>R. Garces Street Brgy. Tunga-tunga City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E72">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F72">
         <is>
-          <t>2/24/1979</t>
+          <t>5/23/1958</t>
         </is>
       </c>
       <c t="inlineStr" r="G72">
@@ -5338,12 +5343,12 @@
       </c>
       <c t="inlineStr" r="H72">
         <is>
-          <t>Trainer</t>
+          <t>Teacher 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I72">
         <is>
-          <t>Pacific Vocational Training Center Inc.</t>
+          <t>Villa Jacinta National Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J72">
@@ -5353,12 +5358,12 @@
       </c>
       <c t="inlineStr" r="K72">
         <is>
-          <t>Cookery NC II</t>
+          <t>Bread and Pastry Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L72">
         <is>
-          <t>TRSCOK21402086426310015</t>
+          <t>TRSBPP20902086426310011</t>
         </is>
       </c>
       <c t="inlineStr" r="M72">
@@ -5368,7 +5373,7 @@
       </c>
       <c t="inlineStr" r="N72">
         <is>
-          <t>4/7/2031</t>
+          <t>1/12/2031</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5390,12 @@
       </c>
       <c t="inlineStr" r="C73">
         <is>
-          <t>Rhett Togonon Binghoy</t>
+          <t>Joel Piso Paler</t>
         </is>
       </c>
       <c t="inlineStr" r="D73">
         <is>
-          <t>Salog Hinunangan Southern Leyte</t>
+          <t>Hitawos Bontoc Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E73">
@@ -5400,47 +5405,47 @@
       </c>
       <c t="inlineStr" r="F73">
         <is>
-          <t>2/24/1979</t>
+          <t>4/18/2001</t>
         </is>
       </c>
       <c t="inlineStr" r="G73">
         <is>
-          <t>College Graduate</t>
+          <t>Post Secondary Non-Tertiary/Technical Vocational Course Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H73">
         <is>
-          <t>Trainer</t>
+          <t>Instructor</t>
         </is>
       </c>
       <c t="inlineStr" r="I73">
         <is>
-          <t>Pacific Vocational Training Center Inc.</t>
+          <t>Farmfinity Resort</t>
         </is>
       </c>
       <c t="inlineStr" r="J73">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K73">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Food and Beverage Services NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L73">
         <is>
-          <t>MEEEAW10601086426290016</t>
+          <t>TRSFBS21302086426310008</t>
         </is>
       </c>
       <c t="inlineStr" r="M73">
         <is>
-          <t>6/8/2026</t>
+          <t>2/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N73">
         <is>
-          <t>7/24/2029</t>
+          <t>2/18/2031</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5462,12 @@
       </c>
       <c t="inlineStr" r="C74">
         <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D74">
         <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E74">
@@ -5472,7 +5477,7 @@
       </c>
       <c t="inlineStr" r="F74">
         <is>
-          <t>6/26/1983</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G74">
@@ -5482,37 +5487,37 @@
       </c>
       <c t="inlineStr" r="H74">
         <is>
-          <t>Administrative Assistant 3</t>
+          <t>School Administrator</t>
         </is>
       </c>
       <c t="inlineStr" r="I74">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>Marsia Fiona Agro - Industrial School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J74">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K74">
         <is>
-          <t>Driving NC II</t>
+          <t>Bread and Pastry Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L74">
         <is>
-          <t>ALTDRV20402086426310017</t>
+          <t>TRSBPP20902086426310009</t>
         </is>
       </c>
       <c t="inlineStr" r="M74">
         <is>
-          <t>6/8/2026</t>
+          <t>2/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N74">
         <is>
-          <t>4/20/2031</t>
+          <t>2/18/2031</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5534,12 @@
       </c>
       <c t="inlineStr" r="C75">
         <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
+          <t>Rhett Togonon Binghoy</t>
         </is>
       </c>
       <c t="inlineStr" r="D75">
         <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
+          <t>Salog Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E75">
@@ -5544,47 +5549,47 @@
       </c>
       <c t="inlineStr" r="F75">
         <is>
-          <t>6/26/1983</t>
+          <t>2/24/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G75">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H75">
         <is>
-          <t>Administrative Assistant 3</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I75">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>Pacific Vocational Training Center Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J75">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K75">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
+          <t>Cookery NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L75">
         <is>
-          <t>MEEEAW20602086426310018</t>
+          <t>TRSCOK21402086426310015</t>
         </is>
       </c>
       <c t="inlineStr" r="M75">
         <is>
-          <t>6/9/2026</t>
+          <t>5/11/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N75">
         <is>
-          <t>4/20/2031</t>
+          <t>4/7/2031</t>
         </is>
       </c>
     </row>
@@ -5601,52 +5606,52 @@
       </c>
       <c t="inlineStr" r="C76">
         <is>
-          <t>Lucia Misal Villarias</t>
+          <t>Ranulfo Datoy Kuizon Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D76">
         <is>
-          <t>Zone 1 Mangkaw Sogod Southern Leyte</t>
+          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E76">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F76">
         <is>
-          <t>12/13/1959</t>
+          <t>6/26/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G76">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H76">
         <is>
-          <t>Trainer</t>
+          <t>Administrative Assistant 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I76">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School Inc.</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J76">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K76">
         <is>
-          <t>Cookery NC II</t>
+          <t>Driving NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L76">
         <is>
-          <t>TRSCOK21402086426290019</t>
+          <t>ALTDRV20402086426310017</t>
         </is>
       </c>
       <c t="inlineStr" r="M76">
@@ -5656,7 +5661,7 @@
       </c>
       <c t="inlineStr" r="N76">
         <is>
-          <t>10/20/2029</t>
+          <t>4/20/2031</t>
         </is>
       </c>
     </row>
@@ -5673,12 +5678,12 @@
       </c>
       <c t="inlineStr" r="C77">
         <is>
-          <t>Edsel Ray Bactul Vallinas</t>
+          <t>Ranulfo Datoy Kuizon Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D77">
         <is>
-          <t>440, I. Paler St.(ext) Tagnipa City of Maasin Southern Leyte</t>
+          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E77">
@@ -5688,335 +5693,47 @@
       </c>
       <c t="inlineStr" r="F77">
         <is>
-          <t>12/15/1998</t>
+          <t>6/26/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G77">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H77">
         <is>
-          <t>Special Science Teacher I</t>
+          <t>Administrative Assistant 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I77">
         <is>
-          <t>Maasin City National High School</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J77">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K77">
         <is>
-          <t>Computer Systems Servicing NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L77">
         <is>
-          <t>ELCCSS21302086426270020</t>
+          <t>MEEEAW20602086426310018</t>
         </is>
       </c>
       <c t="inlineStr" r="M77">
         <is>
-          <t>6/8/2026</t>
+          <t>6/9/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N77">
         <is>
-          <t>10/27/2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c t="inlineStr" r="A78">
-        <is>
-          <t>Region VIII - Eastern Visayas</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B78">
-        <is>
-          <t>Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C78">
-        <is>
-          <t>Eduardo Lora Bosque</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D78">
-        <is>
-          <t>San Rafael City of Maasin Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E78">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F78">
-        <is>
-          <t>3/27/1987</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G78">
-        <is>
-          <t>College Undergraduate</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H78">
-        <is>
-          <t>Head Mechanic</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I78">
-        <is>
-          <t>Phil Auto Citi Services Inc</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J78">
-        <is>
-          <t>Automotive and Land Transportation</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="K78">
-        <is>
-          <t>Automotive Servicing NC I</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L78">
-        <is>
-          <t>ALTATS11801086426290021</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M78">
-        <is>
-          <t>6/25/2026</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N78">
-        <is>
-          <t>5/15/2029</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c t="inlineStr" r="A79">
-        <is>
-          <t>Region VIII - Eastern Visayas</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B79">
-        <is>
-          <t>Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C79">
-        <is>
-          <t>Joedee Mark . Rodriguez</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D79">
-        <is>
-          <t>Brgy. San Jose Sogod Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E79">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F79">
-        <is>
-          <t>1/20/1995</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G79">
-        <is>
-          <t>College Graduate</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H79">
-        <is>
-          <t>Ac Manager</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I79">
-        <is>
-          <t>Southern Leyte Stete University</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J79">
-        <is>
-          <t>Electrical and Electronics</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="K79">
-        <is>
-          <t>Computer Systems Servicing NC II</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L79">
-        <is>
-          <t>ELCCSS21302086426300022</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M79">
-        <is>
-          <t>6/25/2026</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N79">
-        <is>
-          <t>10/22/2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c t="inlineStr" r="A80">
-        <is>
-          <t>Region VIII - Eastern Visayas</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B80">
-        <is>
-          <t>Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C80">
-        <is>
-          <t>Lucia Misal Villarias</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D80">
-        <is>
-          <t>Zone 1 Mangkaw Sogod Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E80">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F80">
-        <is>
-          <t>12/13/1959</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G80">
-        <is>
-          <t>College Graduate</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H80">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I80">
-        <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J80">
-        <is>
-          <t>Tourism (Hotel and Restaurant)</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="K80">
-        <is>
-          <t>Housekeeping NC II</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L80">
-        <is>
-          <t>TRSHSK21302086426300023</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M80">
-        <is>
-          <t>9/2/2026</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N80">
-        <is>
-          <t>12/4/2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c t="inlineStr" r="A81">
-        <is>
-          <t>Region VIII - Eastern Visayas</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B81">
-        <is>
-          <t>Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C81">
-        <is>
-          <t>Cerecio Cabudbud Mendoza</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D81">
-        <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E81">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F81">
-        <is>
-          <t>2/21/1960</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G81">
-        <is>
-          <t>Masteral</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H81">
-        <is>
-          <t>Maintenance Head</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I81">
-        <is>
-          <t>Ghrace Jhoy Technical And Vocational School</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J81">
-        <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="K81">
-        <is>
-          <t>Plumbing NC II</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L81">
-        <is>
-          <t>CONPLM21402086426280024</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M81">
-        <is>
-          <t>9/2/2026</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N81">
-        <is>
-          <t>5/24/2028</t>
+          <t>4/20/2031</t>
         </is>
       </c>
     </row>

--- a/data/excel/competency_assessors.xlsx
+++ b/data/excel/competency_assessors.xlsx
@@ -298,62 +298,62 @@
       </c>
       <c t="inlineStr" r="C2">
         <is>
-          <t>Allen Dolorito Monter</t>
+          <t>Almira Leonor Miras</t>
         </is>
       </c>
       <c t="inlineStr" r="D2">
         <is>
-          <t>Asuncion City of Maasin Southern Leyte</t>
+          <t>Brgy. Laboon City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E2">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F2">
         <is>
-          <t>9/18/1990</t>
+          <t>2/6/1972</t>
         </is>
       </c>
       <c t="inlineStr" r="G2">
         <is>
-          <t>College Undergraduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H2">
         <is>
-          <t>Cac Support Staff</t>
+          <t>School Nurse/competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I2">
         <is>
-          <t>Tesda So. Leyte Provincial Office</t>
+          <t>Saint Joseph College</t>
         </is>
       </c>
       <c t="inlineStr" r="J2">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Human Health / Health Care</t>
         </is>
       </c>
       <c t="inlineStr" r="K2">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Health Care Services NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L2">
         <is>
-          <t>CA-BPP0208642126013</t>
+          <t>CA-HCS0208642226001</t>
         </is>
       </c>
       <c t="inlineStr" r="M2">
         <is>
-          <t>11/17/2021</t>
+          <t>1/14/2022</t>
         </is>
       </c>
       <c t="inlineStr" r="N2">
         <is>
-          <t>10/21/2026</t>
+          <t>11/17/2026</t>
         </is>
       </c>
     </row>
@@ -370,62 +370,62 @@
       </c>
       <c t="inlineStr" r="C3">
         <is>
-          <t>Almira Leonor Miras</t>
+          <t>Arnaldo Binalangbang Salem</t>
         </is>
       </c>
       <c t="inlineStr" r="D3">
         <is>
-          <t>Brgy. Laboon City of Maasin Southern Leyte</t>
+          <t>Tigbao Libagon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E3">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t>2/6/1972</t>
+          <t>6/5/1981</t>
         </is>
       </c>
       <c t="inlineStr" r="G3">
         <is>
-          <t>Masteral</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t>School Nurse/competency Assessor</t>
+          <t>Farm Owner/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I3">
         <is>
-          <t>Saint Joseph College</t>
+          <t>A.i Integrated Farm School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J3">
         <is>
-          <t>Human Health / Health Care</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K3">
         <is>
-          <t>Health Care Services NC II</t>
+          <t>Rice Machinery Operations NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L3">
         <is>
-          <t>CA-HCS0208642226001</t>
+          <t>CA-RMO0208642326007</t>
         </is>
       </c>
       <c t="inlineStr" r="M3">
         <is>
-          <t>1/14/2022</t>
+          <t>6/30/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N3">
         <is>
-          <t>11/17/2026</t>
+          <t>11/18/2026</t>
         </is>
       </c>
     </row>
@@ -442,12 +442,12 @@
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t>Arnaldo Binalangbang Salem</t>
+          <t>Kierzner Dounee Ordiz Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D4">
         <is>
-          <t>Tigbao Libagon Southern Leyte</t>
+          <t>Mambajao City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E4">
@@ -457,7 +457,7 @@
       </c>
       <c t="inlineStr" r="F4">
         <is>
-          <t>6/5/1981</t>
+          <t>3/30/1996</t>
         </is>
       </c>
       <c t="inlineStr" r="G4">
@@ -467,37 +467,37 @@
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t>Farm Owner/assessor</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I4">
         <is>
-          <t>A.i Integrated Farm School, Inc.</t>
+          <t>Private/on-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Human Health / Health Care</t>
         </is>
       </c>
       <c t="inlineStr" r="K4">
         <is>
-          <t>Rice Machinery Operations NC II</t>
+          <t>Caregiving NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L4">
         <is>
-          <t>CA-RMO0208642326007</t>
+          <t>CA-CGV0208642326015</t>
         </is>
       </c>
       <c t="inlineStr" r="M4">
         <is>
-          <t>6/30/2023</t>
+          <t>11/3/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N4">
         <is>
-          <t>11/18/2026</t>
+          <t>11/29/2026</t>
         </is>
       </c>
     </row>
@@ -514,12 +514,12 @@
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t>Kierzner Dounee Ordiz Caores</t>
+          <t>Harris Zabala Aguilando</t>
         </is>
       </c>
       <c t="inlineStr" r="D5">
         <is>
-          <t>Mambajao City of Maasin Southern Leyte</t>
+          <t>Las Navas Northern Samar</t>
         </is>
       </c>
       <c t="inlineStr" r="E5">
@@ -529,7 +529,7 @@
       </c>
       <c t="inlineStr" r="F5">
         <is>
-          <t>3/30/1996</t>
+          <t>8/23/1977</t>
         </is>
       </c>
       <c t="inlineStr" r="G5">
@@ -539,37 +539,37 @@
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t>Competency Assessor</t>
+          <t>Sr. Tesd Specialist</t>
         </is>
       </c>
       <c t="inlineStr" r="I5">
         <is>
-          <t>Private/on-call</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
         <is>
-          <t>Human Health / Health Care</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K5">
         <is>
-          <t>Caregiving NC II</t>
+          <t>Animal Production (Ruminants) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L5">
         <is>
-          <t>CA-CGV0208642326015</t>
+          <t>AFFAPR21302086425260010</t>
         </is>
       </c>
       <c t="inlineStr" r="M5">
         <is>
-          <t>11/3/2023</t>
+          <t>8/22/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N5">
         <is>
-          <t>11/29/2026</t>
+          <t>11/30/2026</t>
         </is>
       </c>
     </row>
@@ -586,12 +586,12 @@
       </c>
       <c t="inlineStr" r="C6">
         <is>
-          <t>Harris Zabala Aguilando</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D6">
         <is>
-          <t>Las Navas Northern Samar</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E6">
@@ -601,7 +601,7 @@
       </c>
       <c t="inlineStr" r="F6">
         <is>
-          <t>8/23/1977</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G6">
@@ -609,39 +609,29 @@
           <t>College Graduate</t>
         </is>
       </c>
-      <c t="inlineStr" r="H6">
-        <is>
-          <t>Sr. Tesd Specialist</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I6">
-        <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
-        </is>
-      </c>
       <c t="inlineStr" r="J6">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>TVET</t>
         </is>
       </c>
       <c t="inlineStr" r="K6">
         <is>
-          <t>Animal Production (Ruminants) NC II</t>
+          <t>Trainers Methodology Level  NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L6">
         <is>
-          <t>AFFAPR21302086425260010</t>
+          <t>TVETRM11101000025260282</t>
         </is>
       </c>
       <c t="inlineStr" r="M6">
         <is>
-          <t>8/22/2025</t>
+          <t>12/6/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N6">
         <is>
-          <t>11/30/2026</t>
+          <t>12/5/2026</t>
         </is>
       </c>
     </row>
@@ -658,22 +648,22 @@
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Marian Ichon Angub</t>
         </is>
       </c>
       <c t="inlineStr" r="D7">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>Punong,  Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F7">
         <is>
-          <t>10/13/1993</t>
+          <t>9/20/1992</t>
         </is>
       </c>
       <c t="inlineStr" r="G7">
@@ -681,29 +671,39 @@
           <t>College Graduate</t>
         </is>
       </c>
+      <c t="inlineStr" r="H7">
+        <is>
+          <t>Competency Assessor</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I7">
+        <is>
+          <t>Sir G.  Integrated Farm</t>
+        </is>
+      </c>
       <c t="inlineStr" r="J7">
         <is>
-          <t>TVET</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K7">
         <is>
-          <t>Trainers Methodology Level  NC I</t>
+          <t>Organic Agriculture Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L7">
         <is>
-          <t>TVETRM11101000025260282</t>
+          <t>CA-OAP0208642427009</t>
         </is>
       </c>
       <c t="inlineStr" r="M7">
         <is>
-          <t>12/6/2025</t>
+          <t>2/28/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N7">
         <is>
-          <t>12/5/2026</t>
+          <t>2/10/2027</t>
         </is>
       </c>
     </row>
@@ -720,62 +720,62 @@
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t>Marian Ichon Angub</t>
+          <t>Erwin Yap Almine</t>
         </is>
       </c>
       <c t="inlineStr" r="D8">
         <is>
-          <t>Punong,  Tomas Oppus Southern Leyte</t>
+          <t>Brgy. Nueva Esperanza Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F8">
         <is>
-          <t>9/20/1992</t>
+          <t>4/25/1988</t>
         </is>
       </c>
       <c t="inlineStr" r="G8">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t>Competency Assessor</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I8">
         <is>
-          <t>Sir G.  Integrated Farm</t>
+          <t>Acedilla Technogical Institute - St. Bernard</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K8">
         <is>
-          <t>Organic Agriculture Production NC II</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L8">
         <is>
-          <t>CA-OAP0208642427009</t>
+          <t>CA-EIM0208642327002</t>
         </is>
       </c>
       <c t="inlineStr" r="M8">
         <is>
-          <t>2/28/2024</t>
+          <t>3/15/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N8">
         <is>
-          <t>2/10/2027</t>
+          <t>3/23/2027</t>
         </is>
       </c>
     </row>
@@ -792,62 +792,62 @@
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t>Erwin Yap Almine</t>
+          <t>Michel Tingcoy Pata</t>
         </is>
       </c>
       <c t="inlineStr" r="D9">
         <is>
-          <t>Brgy. Nueva Esperanza Hinunangan Southern Leyte</t>
+          <t>Mahayahay Bontoc Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E9">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F9">
         <is>
-          <t>4/25/1988</t>
+          <t>8/24/1980</t>
         </is>
       </c>
       <c t="inlineStr" r="G9">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t>Trainer</t>
+          <t>Teacher 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I9">
         <is>
-          <t>Acedilla Technogical Institute - St. Bernard</t>
+          <t>Villa Jacinta National Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J9">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Garments</t>
         </is>
       </c>
       <c t="inlineStr" r="K9">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Dressmaking NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L9">
         <is>
-          <t>CA-EIM0208642327002</t>
+          <t>GRMDRM20502086426270004</t>
         </is>
       </c>
       <c t="inlineStr" r="M9">
         <is>
-          <t>3/15/2023</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N9">
         <is>
-          <t>3/23/2027</t>
+          <t>5/3/2027</t>
         </is>
       </c>
     </row>
@@ -864,22 +864,22 @@
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t>Michel Tingcoy Pata</t>
+          <t>Edsel Ray Bactul Vallinas</t>
         </is>
       </c>
       <c t="inlineStr" r="D10">
         <is>
-          <t>Mahayahay Bontoc Southern Leyte</t>
+          <t>440, I. Paler St.(ext) Tagnipa City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F10">
         <is>
-          <t>8/24/1980</t>
+          <t>12/15/1998</t>
         </is>
       </c>
       <c t="inlineStr" r="G10">
@@ -889,37 +889,37 @@
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t>Teacher 3</t>
+          <t>Special Science Teacher I</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
         <is>
-          <t>Villa Jacinta National Vocational High School</t>
+          <t>Maasin City National High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
         <is>
-          <t>Garments</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K10">
         <is>
-          <t>Dressmaking NC II</t>
+          <t>Computer Systems Servicing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L10">
         <is>
-          <t>GRMDRM20502086426270004</t>
+          <t>ELCCSS21302086426270020</t>
         </is>
       </c>
       <c t="inlineStr" r="M10">
         <is>
-          <t>1/23/2026</t>
+          <t>6/8/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N10">
         <is>
-          <t>5/3/2027</t>
+          <t>10/27/2027</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t>Edsel Ray Bactul Vallinas</t>
+          <t>Amiel Lora Bosque</t>
         </is>
       </c>
       <c t="inlineStr" r="D11">
         <is>
-          <t>440, I. Paler St.(ext) Tagnipa City of Maasin Southern Leyte</t>
+          <t>Brgy. San Rafael City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E11">
@@ -951,47 +951,47 @@
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t>12/15/1998</t>
+          <t>10/11/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G11">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t>Special Science Teacher I</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I11">
         <is>
-          <t>Maasin City National High School</t>
+          <t>St. Thomas Aquinas College, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J11">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K11">
         <is>
-          <t>Computer Systems Servicing NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L11">
         <is>
-          <t>ELCCSS21302086426270020</t>
+          <t>CA-EAW0108642427004</t>
         </is>
       </c>
       <c t="inlineStr" r="M11">
         <is>
-          <t>6/8/2026</t>
+          <t>2/26/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N11">
         <is>
-          <t>10/27/2027</t>
+          <t>11/10/2027</t>
         </is>
       </c>
     </row>
@@ -1008,52 +1008,52 @@
       </c>
       <c t="inlineStr" r="C12">
         <is>
-          <t>Amiel Lora Bosque</t>
+          <t>Lerma Caña Parado</t>
         </is>
       </c>
       <c t="inlineStr" r="D12">
         <is>
-          <t>Brgy. San Rafael City of Maasin Southern Leyte</t>
+          <t>Real Street Poblacion Julita Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E12">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F12">
         <is>
-          <t>10/11/1983</t>
+          <t>1/24/1978</t>
         </is>
       </c>
       <c t="inlineStr" r="G12">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I12">
         <is>
-          <t>St. Thomas Aquinas College, Inc.</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J12">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K12">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Agroentrepreneurship NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L12">
         <is>
-          <t>CA-EAW0108642427004</t>
+          <t>CA-AGE0208642427005</t>
         </is>
       </c>
       <c t="inlineStr" r="M12">
@@ -1063,7 +1063,7 @@
       </c>
       <c t="inlineStr" r="N12">
         <is>
-          <t>11/10/2027</t>
+          <t>12/7/2027</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c t="inlineStr" r="C13">
         <is>
-          <t>Lerma Caña Parado</t>
+          <t>Ma. Asuncion Bagolor Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D13">
         <is>
-          <t>Real Street Poblacion Julita Leyte</t>
+          <t>Brgy. Dongon City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E13">
@@ -1095,47 +1095,47 @@
       </c>
       <c t="inlineStr" r="F13">
         <is>
-          <t>1/24/1978</t>
+          <t>8/10/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G13">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t>Competency Assessor</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I13">
         <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
+          <t>The College Of Maasin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K13">
         <is>
-          <t>Agroentrepreneurship NC II</t>
+          <t>Bread and Pastry Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L13">
         <is>
-          <t>CA-AGE0208642427005</t>
+          <t>CA-BPP0208642428010</t>
         </is>
       </c>
       <c t="inlineStr" r="M13">
         <is>
-          <t>2/26/2024</t>
+          <t>2/28/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N13">
         <is>
-          <t>12/7/2027</t>
+          <t>1/8/2028</t>
         </is>
       </c>
     </row>
@@ -1152,22 +1152,22 @@
       </c>
       <c t="inlineStr" r="C14">
         <is>
-          <t>Ma. Asuncion Bagolor Mendoza</t>
+          <t>Roger . Ladica .</t>
         </is>
       </c>
       <c t="inlineStr" r="D14">
         <is>
-          <t>Brgy. Dongon City of Maasin Southern Leyte</t>
+          <t>Ponong Bato Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F14">
         <is>
-          <t>8/10/1979</t>
+          <t>3/2/1976</t>
         </is>
       </c>
       <c t="inlineStr" r="G14">
@@ -1177,37 +1177,37 @@
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I14">
         <is>
-          <t>The College Of Maasin, Inc.</t>
+          <t>On-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K14">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L14">
         <is>
-          <t>CA-BPP0208642428010</t>
+          <t>CA-EAW0108642328004</t>
         </is>
       </c>
       <c t="inlineStr" r="M14">
         <is>
-          <t>2/28/2024</t>
+          <t>3/17/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N14">
         <is>
-          <t>1/8/2028</t>
+          <t>1/11/2028</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t>Roger . Ladica .</t>
+          <t>Ricky Zafra Tapal</t>
         </is>
       </c>
       <c t="inlineStr" r="D15">
         <is>
-          <t>Ponong Bato Leyte</t>
+          <t>Baranggay Salog,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E15">
@@ -1239,22 +1239,22 @@
       </c>
       <c t="inlineStr" r="F15">
         <is>
-          <t>3/2/1976</t>
+          <t>1/12/1985</t>
         </is>
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t>Trainer</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I15">
         <is>
-          <t>On-call</t>
+          <t>N/a</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
@@ -1264,22 +1264,22 @@
       </c>
       <c t="inlineStr" r="K15">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L15">
         <is>
-          <t>CA-EAW0108642328004</t>
+          <t>CA-EAW0208642328014</t>
         </is>
       </c>
       <c t="inlineStr" r="M15">
         <is>
-          <t>3/17/2023</t>
+          <t>8/3/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N15">
         <is>
-          <t>1/11/2028</t>
+          <t>2/6/2028</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c t="inlineStr" r="C16">
         <is>
-          <t>Ricky Zafra Tapal</t>
+          <t>Arnaldo Binalangbang Salem</t>
         </is>
       </c>
       <c t="inlineStr" r="D16">
         <is>
-          <t>Baranggay Salog,  Hinunangan Southern Leyte</t>
+          <t>Tigbao Libagon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E16">
@@ -1311,7 +1311,7 @@
       </c>
       <c t="inlineStr" r="F16">
         <is>
-          <t>1/12/1985</t>
+          <t>6/5/1981</t>
         </is>
       </c>
       <c t="inlineStr" r="G16">
@@ -1321,37 +1321,37 @@
       </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Farm Owner/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I16">
         <is>
-          <t>N/a</t>
+          <t>A.i Integrated Farm School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J16">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K16">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
+          <t>Organic Agriculture Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L16">
         <is>
-          <t>CA-EAW0208642328014</t>
+          <t>CA-OAP0208642328006</t>
         </is>
       </c>
       <c t="inlineStr" r="M16">
         <is>
-          <t>8/3/2023</t>
+          <t>6/30/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N16">
         <is>
-          <t>2/6/2028</t>
+          <t>3/28/2028</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c t="inlineStr" r="C17">
         <is>
-          <t>Arnaldo Binalangbang Salem</t>
+          <t>Cerecio Cabudbud Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D17">
         <is>
-          <t>Tigbao Libagon Southern Leyte</t>
+          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E17">
@@ -1383,37 +1383,32 @@
       </c>
       <c t="inlineStr" r="F17">
         <is>
-          <t>6/5/1981</t>
+          <t>2/21/1960</t>
         </is>
       </c>
       <c t="inlineStr" r="G17">
         <is>
-          <t>College Graduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t>Farm Owner/assessor</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I17">
-        <is>
-          <t>A.i Integrated Farm School, Inc.</t>
+          <t>Retired School Head Teacher/on Call Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K17">
         <is>
-          <t>Organic Agriculture Production NC II</t>
+          <t>Driving NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L17">
         <is>
-          <t>CA-OAP0208642328006</t>
+          <t>CA-DRV0208642328008</t>
         </is>
       </c>
       <c t="inlineStr" r="M17">
@@ -1423,7 +1418,7 @@
       </c>
       <c t="inlineStr" r="N17">
         <is>
-          <t>3/28/2028</t>
+          <t>4/2/2028</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1435,12 @@
       </c>
       <c t="inlineStr" r="C18">
         <is>
-          <t>Cerecio Cabudbud Mendoza</t>
+          <t>Michael Mostaza Diaz</t>
         </is>
       </c>
       <c t="inlineStr" r="D18">
         <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
+          <t>76 A. Luna Street  City of Baybay Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E18">
@@ -1455,32 +1450,37 @@
       </c>
       <c t="inlineStr" r="F18">
         <is>
-          <t>2/21/1960</t>
+          <t>4/24/1985</t>
         </is>
       </c>
       <c t="inlineStr" r="G18">
         <is>
-          <t>Masteral</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t>Retired School Head Teacher/on Call Trainer/assessor</t>
+          <t>Competency Assessor</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I18">
+        <is>
+          <t>Freelancer</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K18">
         <is>
-          <t>Driving NC II</t>
+          <t>Events Management Services NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L18">
         <is>
-          <t>CA-DRV0208642328008</t>
+          <t>CA-EVM0308642328010</t>
         </is>
       </c>
       <c t="inlineStr" r="M18">
@@ -1490,7 +1490,7 @@
       </c>
       <c t="inlineStr" r="N18">
         <is>
-          <t>4/2/2028</t>
+          <t>4/16/2028</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c t="inlineStr" r="C19">
         <is>
-          <t>Michael Mostaza Diaz</t>
+          <t>Rhett Togonon Binghoy</t>
         </is>
       </c>
       <c t="inlineStr" r="D19">
         <is>
-          <t>76 A. Luna Street  City of Baybay Leyte</t>
+          <t>Salog Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E19">
@@ -1522,7 +1522,7 @@
       </c>
       <c t="inlineStr" r="F19">
         <is>
-          <t>4/24/1985</t>
+          <t>2/24/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G19">
@@ -1532,37 +1532,37 @@
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t>Competency Assessor</t>
+          <t>Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I19">
         <is>
-          <t>Freelancer</t>
+          <t>Pacific Vocational Training Center, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K19">
         <is>
-          <t>Events Management Services NC III</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L19">
         <is>
-          <t>CA-EVM0308642328010</t>
+          <t>CA-EAW0208642328012</t>
         </is>
       </c>
       <c t="inlineStr" r="M19">
         <is>
-          <t>6/30/2023</t>
+          <t>8/3/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N19">
         <is>
-          <t>4/16/2028</t>
+          <t>5/4/2028</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c t="inlineStr" r="C20">
         <is>
-          <t>Rhett Togonon Binghoy</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D20">
         <is>
-          <t>Salog Hinunangan Southern Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E20">
@@ -1594,47 +1594,47 @@
       </c>
       <c t="inlineStr" r="F20">
         <is>
-          <t>2/24/1979</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G20">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t>Assessor</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I20">
         <is>
-          <t>Pacific Vocational Training Center, Inc.</t>
+          <t>Liz Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K20">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
+          <t>Organic Agriculture Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L20">
         <is>
-          <t>CA-EAW0208642328012</t>
+          <t>CA-OAP0208642328019</t>
         </is>
       </c>
       <c t="inlineStr" r="M20">
         <is>
-          <t>8/3/2023</t>
+          <t>11/30/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N20">
         <is>
-          <t>5/4/2028</t>
+          <t>5/15/2028</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c t="inlineStr" r="C21">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Marven Dejarme Estinozo</t>
         </is>
       </c>
       <c t="inlineStr" r="D21">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Brgy. Consolacion Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E21">
@@ -1666,47 +1666,47 @@
       </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t>4/7/1969</t>
+          <t>1/3/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G21">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t>Competency Assessor</t>
+          <t>Head Computer Technician</t>
         </is>
       </c>
       <c t="inlineStr" r="I21">
         <is>
-          <t>Liz Integrated Farm</t>
+          <t>Arc Tutorials Learning Services Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J21">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K21">
         <is>
-          <t>Organic Agriculture Production NC II</t>
+          <t>Computer Systems Servicing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L21">
         <is>
-          <t>CA-OAP0208642328019</t>
+          <t>ELCCSS21302086424280008</t>
         </is>
       </c>
       <c t="inlineStr" r="M21">
         <is>
-          <t>11/30/2023</t>
+          <t>10/24/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N21">
         <is>
-          <t>5/15/2028</t>
+          <t>5/18/2028</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c t="inlineStr" r="C22">
         <is>
-          <t>Marven Dejarme Estinozo</t>
+          <t>Cerecio Cabudbud Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D22">
         <is>
-          <t>Brgy. Consolacion Sogod Southern Leyte</t>
+          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E22">
@@ -1738,47 +1738,47 @@
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t>1/3/1983</t>
+          <t>2/21/1960</t>
         </is>
       </c>
       <c t="inlineStr" r="G22">
         <is>
-          <t>College Graduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t>Head Computer Technician</t>
+          <t>Maintenance Head</t>
         </is>
       </c>
       <c t="inlineStr" r="I22">
         <is>
-          <t>Arc Tutorials Learning Services Inc.</t>
+          <t>Ghrace Jhoy Technical And Vocational School</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K22">
         <is>
-          <t>Computer Systems Servicing NC II</t>
+          <t>Plumbing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L22">
         <is>
-          <t>ELCCSS21302086424280008</t>
+          <t>CONPLM21402086426280024</t>
         </is>
       </c>
       <c t="inlineStr" r="M22">
         <is>
-          <t>10/24/2024</t>
+          <t>9/2/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N22">
         <is>
-          <t>5/18/2028</t>
+          <t>5/24/2028</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c t="inlineStr" r="C23">
         <is>
-          <t>Cerecio Cabudbud Mendoza</t>
+          <t>Ghubert Fedival Francisco</t>
         </is>
       </c>
       <c t="inlineStr" r="D23">
         <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
+          <t>Brgy. 91 Abucay Tacloban City Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E23">
@@ -1810,47 +1810,47 @@
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t>2/21/1960</t>
+          <t>6/28/1976</t>
         </is>
       </c>
       <c t="inlineStr" r="G23">
         <is>
-          <t>Masteral</t>
+          <t>Doctorate</t>
         </is>
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t>Maintenance Head</t>
+          <t>Trainer/competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School</t>
+          <t>Ghrace Jhoy Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
         <is>
-          <t>Construction</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K23">
         <is>
-          <t>Plumbing NC II</t>
+          <t>Agricultural Crops Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L23">
         <is>
-          <t>CONPLM21402086426280024</t>
+          <t>CA-ACP0208642328017</t>
         </is>
       </c>
       <c t="inlineStr" r="M23">
         <is>
-          <t>9/2/2026</t>
+          <t>11/28/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N23">
         <is>
-          <t>5/24/2028</t>
+          <t>5/25/2028</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t>Ghubert Fedival Francisco</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D24">
         <is>
-          <t>Brgy. 91 Abucay Tacloban City Leyte</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E24">
@@ -1882,12 +1882,12 @@
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t>6/28/1976</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G24">
         <is>
-          <t>Doctorate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H24">
@@ -1912,7 +1912,7 @@
       </c>
       <c t="inlineStr" r="L24">
         <is>
-          <t>CA-ACP0208642328017</t>
+          <t>CA-ACP0208642328018</t>
         </is>
       </c>
       <c t="inlineStr" r="M24">
@@ -1939,12 +1939,12 @@
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Ricky Zafra Tapal</t>
         </is>
       </c>
       <c t="inlineStr" r="D25">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>Baranggay Salog,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E25">
@@ -1954,7 +1954,7 @@
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t>10/13/1993</t>
+          <t>1/12/1985</t>
         </is>
       </c>
       <c t="inlineStr" r="G25">
@@ -1964,37 +1964,37 @@
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t>Trainer/competency Assessor</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
         <is>
-          <t>Ghrace Jhoy Integrated Farm</t>
+          <t>N/a</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K25">
         <is>
-          <t>Agricultural Crops Production NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L25">
         <is>
-          <t>CA-ACP0208642328018</t>
+          <t>CA-EAW0108642328013</t>
         </is>
       </c>
       <c t="inlineStr" r="M25">
         <is>
-          <t>11/28/2023</t>
+          <t>8/3/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N25">
         <is>
-          <t>5/25/2028</t>
+          <t>6/22/2028</t>
         </is>
       </c>
     </row>
@@ -2011,22 +2011,22 @@
       </c>
       <c t="inlineStr" r="C26">
         <is>
-          <t>Ricky Zafra Tapal</t>
+          <t>Carmelyn Oppus Liberato</t>
         </is>
       </c>
       <c t="inlineStr" r="D26">
         <is>
-          <t>Baranggay Salog,  Hinunangan Southern Leyte</t>
+          <t>Brgy. Maanyag  Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t>1/12/1985</t>
+          <t>1/8/1998</t>
         </is>
       </c>
       <c t="inlineStr" r="G26">
@@ -2036,37 +2036,37 @@
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I26">
         <is>
-          <t>N/a</t>
+          <t>Ghrace Joy Technical And Vocational School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K26">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Food and Beverage Services NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L26">
         <is>
-          <t>CA-EAW0108642328013</t>
+          <t>TRSFBS21302086426280010</t>
         </is>
       </c>
       <c t="inlineStr" r="M26">
         <is>
-          <t>8/3/2023</t>
+          <t>2/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N26">
         <is>
-          <t>6/22/2028</t>
+          <t>6/28/2028</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t>Carmelyn Oppus Liberato</t>
+          <t>Lerma Caña Parado</t>
         </is>
       </c>
       <c t="inlineStr" r="D27">
         <is>
-          <t>Brgy. Maanyag  Tomas Oppus Southern Leyte</t>
+          <t>Real Street Poblacion Julita Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E27">
@@ -2098,7 +2098,7 @@
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t>1/8/1998</t>
+          <t>1/24/1978</t>
         </is>
       </c>
       <c t="inlineStr" r="G27">
@@ -2108,12 +2108,12 @@
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t>Trainer</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I27">
         <is>
-          <t>Ghrace Joy Technical And Vocational School Inc.</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
@@ -2123,22 +2123,22 @@
       </c>
       <c t="inlineStr" r="K27">
         <is>
-          <t>Food and Beverage Services NC II</t>
+          <t>Events Management Services NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L27">
         <is>
-          <t>TRSFBS21302086426280010</t>
+          <t>CA-EVM0308642428002</t>
         </is>
       </c>
       <c t="inlineStr" r="M27">
         <is>
-          <t>2/20/2026</t>
+          <t>1/5/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N27">
         <is>
-          <t>6/28/2028</t>
+          <t>6/29/2028</t>
         </is>
       </c>
     </row>
@@ -2155,22 +2155,22 @@
       </c>
       <c t="inlineStr" r="C28">
         <is>
-          <t>Lerma Caña Parado</t>
+          <t>Gaudencio Regaton Saratan Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D28">
         <is>
-          <t>Real Street Poblacion Julita Leyte</t>
+          <t>168 Rosales Street Brgy. Tagnipa City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E28">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F28">
         <is>
-          <t>1/24/1978</t>
+          <t>6/14/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G28">
@@ -2180,37 +2180,37 @@
       </c>
       <c t="inlineStr" r="H28">
         <is>
-          <t>Competency Assessor</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I28">
         <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
+          <t>On-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J28">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K28">
         <is>
-          <t>Events Management Services NC III</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L28">
         <is>
-          <t>CA-EVM0308642428002</t>
+          <t>CA-EIM0208642428011</t>
         </is>
       </c>
       <c t="inlineStr" r="M28">
         <is>
-          <t>1/5/2024</t>
+          <t>2/28/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N28">
         <is>
-          <t>6/29/2028</t>
+          <t>8/24/2028</t>
         </is>
       </c>
     </row>
@@ -2227,12 +2227,12 @@
       </c>
       <c t="inlineStr" r="C29">
         <is>
-          <t>Gaudencio Regaton Saratan Jr.</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D29">
         <is>
-          <t>168 Rosales Street Brgy. Tagnipa City of Maasin Southern Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E29">
@@ -2242,22 +2242,22 @@
       </c>
       <c t="inlineStr" r="F29">
         <is>
-          <t>6/14/1969</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G29">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H29">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I29">
         <is>
-          <t>On-call</t>
+          <t>On-call (private)</t>
         </is>
       </c>
       <c t="inlineStr" r="J29">
@@ -2272,17 +2272,17 @@
       </c>
       <c t="inlineStr" r="L29">
         <is>
-          <t>CA-EIM0208642428011</t>
+          <t>CA-EIM0208642328016</t>
         </is>
       </c>
       <c t="inlineStr" r="M29">
         <is>
-          <t>2/28/2024</t>
+          <t>11/28/2023</t>
         </is>
       </c>
       <c t="inlineStr" r="N29">
         <is>
-          <t>8/24/2028</t>
+          <t>9/24/2028</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c t="inlineStr" r="C30">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Ranulfo Datoy Kuizon Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D30">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E30">
@@ -2314,7 +2314,7 @@
       </c>
       <c t="inlineStr" r="F30">
         <is>
-          <t>4/7/1969</t>
+          <t>6/26/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G30">
@@ -2324,37 +2324,37 @@
       </c>
       <c t="inlineStr" r="H30">
         <is>
-          <t>Competency Assessor</t>
+          <t>Trainer/assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I30">
         <is>
-          <t>On-call (private)</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J30">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K30">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>PV Systems Installation NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L30">
         <is>
-          <t>CA-EIM0208642328016</t>
+          <t>CA-PVI0208642428012</t>
         </is>
       </c>
       <c t="inlineStr" r="M30">
         <is>
-          <t>11/28/2023</t>
+          <t>2/28/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N30">
         <is>
-          <t>9/24/2028</t>
+          <t>10/12/2028</t>
         </is>
       </c>
     </row>
@@ -2406,27 +2406,27 @@
       </c>
       <c t="inlineStr" r="J31">
         <is>
-          <t>Construction</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K31">
         <is>
-          <t>PV Systems Installation NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L31">
         <is>
-          <t>CA-PVI0208642428012</t>
+          <t>CA-EAW0108642428003</t>
         </is>
       </c>
       <c t="inlineStr" r="M31">
         <is>
-          <t>2/28/2024</t>
+          <t>1/5/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N31">
         <is>
-          <t>10/12/2028</t>
+          <t>11/15/2028</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c t="inlineStr" r="C32">
         <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D32">
         <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E32">
@@ -2458,7 +2458,7 @@
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t>6/26/1983</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
@@ -2468,37 +2468,37 @@
       </c>
       <c t="inlineStr" r="H32">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Accredited Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I32">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>On-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J32">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K32">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Agricultural Crops Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L32">
         <is>
-          <t>CA-EAW0108642428003</t>
+          <t>CA-ACP0208642428019</t>
         </is>
       </c>
       <c t="inlineStr" r="M32">
         <is>
-          <t>1/5/2024</t>
+          <t>4/30/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N32">
         <is>
-          <t>11/15/2028</t>
+          <t>11/18/2028</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c t="inlineStr" r="C33">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Esmeraldo Palazon Orail Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D33">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Mahayahay Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E33">
@@ -2530,47 +2530,47 @@
       </c>
       <c t="inlineStr" r="F33">
         <is>
-          <t>4/7/1969</t>
+          <t>10/6/1981</t>
         </is>
       </c>
       <c t="inlineStr" r="G33">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H33">
         <is>
-          <t>Accredited Competency Assessor</t>
+          <t>Company Driver</t>
         </is>
       </c>
       <c t="inlineStr" r="I33">
         <is>
-          <t>On-call</t>
+          <t>Ghraze Jhoy Techncial Vocational School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J33">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K33">
         <is>
-          <t>Agricultural Crops Production NC II</t>
+          <t>Driving (Passenger Bus/Straight Truck) NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L33">
         <is>
-          <t>CA-ACP0208642428019</t>
+          <t>ALTDRB31103086425280016</t>
         </is>
       </c>
       <c t="inlineStr" r="M33">
         <is>
-          <t>4/30/2024</t>
+          <t>8/29/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N33">
         <is>
-          <t>11/18/2028</t>
+          <t>12/3/2028</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c t="inlineStr" r="C34">
         <is>
-          <t>Esmeraldo Palazon Orail Jr.</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D34">
         <is>
-          <t>Mahayahay Sogod Southern Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E34">
@@ -2602,47 +2602,42 @@
       </c>
       <c t="inlineStr" r="F34">
         <is>
-          <t>10/6/1981</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G34">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H34">
         <is>
-          <t>Company Driver</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I34">
-        <is>
-          <t>Ghraze Jhoy Techncial Vocational School Inc.</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="J34">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K34">
         <is>
-          <t>Driving (Passenger Bus/Straight Truck) NC III</t>
+          <t>Animal Production (Poultry-Chicken) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L34">
         <is>
-          <t>ALTDRB31103086425280016</t>
+          <t>CA-APP0208642428018</t>
         </is>
       </c>
       <c t="inlineStr" r="M34">
         <is>
-          <t>8/29/2025</t>
+          <t>4/16/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N34">
         <is>
-          <t>12/3/2028</t>
+          <t>12/6/2028</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2654,12 @@
       </c>
       <c t="inlineStr" r="C35">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Ghubert Fedival Francisco</t>
         </is>
       </c>
       <c t="inlineStr" r="D35">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Brgy. 91 Abucay Tacloban City Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E35">
@@ -2674,42 +2669,47 @@
       </c>
       <c t="inlineStr" r="F35">
         <is>
-          <t>4/7/1969</t>
+          <t>6/28/1976</t>
         </is>
       </c>
       <c t="inlineStr" r="G35">
         <is>
-          <t>College Undergraduate</t>
+          <t>Doctorate</t>
         </is>
       </c>
       <c t="inlineStr" r="H35">
         <is>
-          <t>Competency Assessor</t>
+          <t>Trainer/assessor</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I35">
+        <is>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J35">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Social, Community Development and Other Services</t>
         </is>
       </c>
       <c t="inlineStr" r="K35">
         <is>
-          <t>Animal Production (Poultry-Chicken) NC II</t>
+          <t>Bookkeeping NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L35">
         <is>
-          <t>CA-APP0208642428018</t>
+          <t>CA-BKP0308642428007</t>
         </is>
       </c>
       <c t="inlineStr" r="M35">
         <is>
-          <t>4/16/2024</t>
+          <t>2/26/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N35">
         <is>
-          <t>12/6/2028</t>
+          <t>12/21/2028</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2726,12 @@
       </c>
       <c t="inlineStr" r="C36">
         <is>
-          <t>Ghubert Fedival Francisco</t>
+          <t>Kierzner Dounee Ordiz Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D36">
         <is>
-          <t>Brgy. 91 Abucay Tacloban City Leyte</t>
+          <t>Mambajao City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E36">
@@ -2741,47 +2741,47 @@
       </c>
       <c t="inlineStr" r="F36">
         <is>
-          <t>6/28/1976</t>
+          <t>3/30/1996</t>
         </is>
       </c>
       <c t="inlineStr" r="G36">
         <is>
-          <t>Doctorate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H36">
         <is>
-          <t>Trainer/assessor</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I36">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
+          <t>On-call</t>
         </is>
       </c>
       <c t="inlineStr" r="J36">
         <is>
-          <t>Social, Community Development and Other Services</t>
+          <t>Human Health / Health Care</t>
         </is>
       </c>
       <c t="inlineStr" r="K36">
         <is>
-          <t>Bookkeeping NC III</t>
+          <t>Health Care Services NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L36">
         <is>
-          <t>CA-BKP0308642428007</t>
+          <t>CA-HCS0208642429001</t>
         </is>
       </c>
       <c t="inlineStr" r="M36">
         <is>
-          <t>2/26/2024</t>
+          <t>1/5/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N36">
         <is>
-          <t>12/21/2028</t>
+          <t>1/3/2029</t>
         </is>
       </c>
     </row>
@@ -2798,12 +2798,12 @@
       </c>
       <c t="inlineStr" r="C37">
         <is>
-          <t>Kierzner Dounee Ordiz Caores</t>
+          <t>Rodolfo Paloma Flores</t>
         </is>
       </c>
       <c t="inlineStr" r="D37">
         <is>
-          <t>Mambajao City of Maasin Southern Leyte</t>
+          <t>Baranggay Gakak,  Libagon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E37">
@@ -2813,7 +2813,7 @@
       </c>
       <c t="inlineStr" r="F37">
         <is>
-          <t>3/30/1996</t>
+          <t>3/2/1961</t>
         </is>
       </c>
       <c t="inlineStr" r="G37">
@@ -2823,37 +2823,37 @@
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t>Competency Assessor</t>
+          <t>Freelancer</t>
         </is>
       </c>
       <c t="inlineStr" r="I37">
         <is>
-          <t>On-call</t>
+          <t>Freelancer</t>
         </is>
       </c>
       <c t="inlineStr" r="J37">
         <is>
-          <t>Human Health / Health Care</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K37">
         <is>
-          <t>Health Care Services NC II</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L37">
         <is>
-          <t>CA-HCS0208642429001</t>
+          <t>ELCEIM21502086425290012</t>
         </is>
       </c>
       <c t="inlineStr" r="M37">
         <is>
-          <t>1/5/2024</t>
+          <t>8/22/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N37">
         <is>
-          <t>1/3/2029</t>
+          <t>2/21/2029</t>
         </is>
       </c>
     </row>
@@ -2870,62 +2870,62 @@
       </c>
       <c t="inlineStr" r="C38">
         <is>
-          <t>Rodolfo Paloma Flores</t>
+          <t>Maria Normida Ordiz Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D38">
         <is>
-          <t>Baranggay Gakak,  Libagon Southern Leyte</t>
+          <t>R. Kangleon Street Brgy. Mambajao,  City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E38">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F38">
         <is>
-          <t>3/2/1961</t>
+          <t>12/6/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G38">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H38">
         <is>
-          <t>Freelancer</t>
+          <t>Competency Assessor</t>
         </is>
       </c>
       <c t="inlineStr" r="I38">
         <is>
-          <t>Freelancer</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J38">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K38">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Cookery NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L38">
         <is>
-          <t>ELCEIM21502086425290012</t>
+          <t>CA-COK0208642429006</t>
         </is>
       </c>
       <c t="inlineStr" r="M38">
         <is>
-          <t>8/22/2025</t>
+          <t>2/26/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N38">
         <is>
-          <t>2/21/2029</t>
+          <t>2/22/2029</t>
         </is>
       </c>
     </row>
@@ -2942,32 +2942,32 @@
       </c>
       <c t="inlineStr" r="C39">
         <is>
-          <t>Maria Normida Ordiz Caores</t>
+          <t>Harris Zabala Aguilando</t>
         </is>
       </c>
       <c t="inlineStr" r="D39">
         <is>
-          <t>R. Kangleon Street Brgy. Mambajao,  City of Maasin Southern Leyte</t>
+          <t>Las Navas Northern Samar</t>
         </is>
       </c>
       <c t="inlineStr" r="E39">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F39">
         <is>
-          <t>12/6/1969</t>
+          <t>8/23/1977</t>
         </is>
       </c>
       <c t="inlineStr" r="G39">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H39">
         <is>
-          <t>Competency Assessor</t>
+          <t>Sr. Tesd Specialist</t>
         </is>
       </c>
       <c t="inlineStr" r="I39">
@@ -2977,27 +2977,27 @@
       </c>
       <c t="inlineStr" r="J39">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K39">
         <is>
-          <t>Cookery NC II</t>
+          <t>Animal Production (Swine) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L39">
         <is>
-          <t>CA-COK0208642429006</t>
+          <t>AFFAPS21302086425290009</t>
         </is>
       </c>
       <c t="inlineStr" r="M39">
         <is>
-          <t>2/26/2024</t>
+          <t>8/22/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N39">
         <is>
-          <t>2/22/2029</t>
+          <t>2/26/2029</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c t="inlineStr" r="C40">
         <is>
-          <t>Harris Zabala Aguilando</t>
+          <t>Orlando Coquilla Paas Sr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D40">
         <is>
-          <t>Las Navas Northern Samar</t>
+          <t>2-a New Ahayag Saint Bernard Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E40">
@@ -3029,7 +3029,7 @@
       </c>
       <c t="inlineStr" r="F40">
         <is>
-          <t>8/23/1977</t>
+          <t>11/9/1973</t>
         </is>
       </c>
       <c t="inlineStr" r="G40">
@@ -3039,37 +3039,37 @@
       </c>
       <c t="inlineStr" r="H40">
         <is>
-          <t>Sr. Tesd Specialist</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c t="inlineStr" r="I40">
         <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
+          <t>Southern Leyte Electric Cooperatie Incorporated</t>
         </is>
       </c>
       <c t="inlineStr" r="J40">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K40">
         <is>
-          <t>Animal Production (Swine) NC II</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L40">
         <is>
-          <t>AFFAPS21302086425290009</t>
+          <t>ELCEIM21502086424290003</t>
         </is>
       </c>
       <c t="inlineStr" r="M40">
         <is>
-          <t>8/22/2025</t>
+          <t>9/9/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N40">
         <is>
-          <t>2/26/2029</t>
+          <t>3/20/2029</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c t="inlineStr" r="C41">
         <is>
-          <t>Orlando Coquilla Paas Sr.</t>
+          <t>Rico Bitor Ampo</t>
         </is>
       </c>
       <c t="inlineStr" r="D41">
         <is>
-          <t>2-a New Ahayag Saint Bernard Southern Leyte</t>
+          <t>Brgy. San Roque Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E41">
@@ -3101,22 +3101,22 @@
       </c>
       <c t="inlineStr" r="F41">
         <is>
-          <t>11/9/1973</t>
+          <t>8/17/1961</t>
         </is>
       </c>
       <c t="inlineStr" r="G41">
         <is>
-          <t>College Graduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H41">
         <is>
-          <t>Electrician</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c t="inlineStr" r="I41">
         <is>
-          <t>Southern Leyte Electric Cooperatie Incorporated</t>
+          <t>Southern Leyte State University - Sogod Campus</t>
         </is>
       </c>
       <c t="inlineStr" r="J41">
@@ -3131,7 +3131,7 @@
       </c>
       <c t="inlineStr" r="L41">
         <is>
-          <t>ELCEIM21502086424290003</t>
+          <t>ELCEIM21502086424290001</t>
         </is>
       </c>
       <c t="inlineStr" r="M41">
@@ -3141,7 +3141,7 @@
       </c>
       <c t="inlineStr" r="N41">
         <is>
-          <t>3/20/2029</t>
+          <t>4/21/2029</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3158,12 @@
       </c>
       <c t="inlineStr" r="C42">
         <is>
-          <t>Rico Bitor Ampo</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D42">
         <is>
-          <t>Brgy. San Roque Sogod Southern Leyte</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E42">
@@ -3173,47 +3173,47 @@
       </c>
       <c t="inlineStr" r="F42">
         <is>
-          <t>8/17/1961</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G42">
         <is>
-          <t>Masteral</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H42">
         <is>
-          <t>Associate Professor</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I42">
         <is>
-          <t>Southern Leyte State University - Sogod Campus</t>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J42">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K42">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Agricultural Crops Production NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L42">
         <is>
-          <t>ELCEIM21502086424290001</t>
+          <t>AFFACP30603086426290005</t>
         </is>
       </c>
       <c t="inlineStr" r="M42">
         <is>
-          <t>9/9/2024</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N42">
         <is>
-          <t>4/21/2029</t>
+          <t>5/2/2029</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c t="inlineStr" r="C43">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Eduardo Lora Bosque</t>
         </is>
       </c>
       <c t="inlineStr" r="D43">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>San Rafael City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E43">
@@ -3245,47 +3245,47 @@
       </c>
       <c t="inlineStr" r="F43">
         <is>
-          <t>10/13/1993</t>
+          <t>3/27/1987</t>
         </is>
       </c>
       <c t="inlineStr" r="G43">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t>Trainer</t>
+          <t>Head Mechanic</t>
         </is>
       </c>
       <c t="inlineStr" r="I43">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
+          <t>Phil Auto Citi Services Inc</t>
         </is>
       </c>
       <c t="inlineStr" r="J43">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K43">
         <is>
-          <t>Agricultural Crops Production NC III</t>
+          <t>Automotive Servicing NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L43">
         <is>
-          <t>AFFACP30603086426290005</t>
+          <t>ALTATS11801086426290021</t>
         </is>
       </c>
       <c t="inlineStr" r="M43">
         <is>
-          <t>1/23/2026</t>
+          <t>6/25/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N43">
         <is>
-          <t>5/2/2029</t>
+          <t>5/15/2029</t>
         </is>
       </c>
     </row>
@@ -3302,62 +3302,62 @@
       </c>
       <c t="inlineStr" r="C44">
         <is>
-          <t>Eduardo Lora Bosque</t>
+          <t>Creliza F. Gamay</t>
         </is>
       </c>
       <c t="inlineStr" r="D44">
         <is>
-          <t>San Rafael City of Maasin Southern Leyte</t>
+          <t>Brgy. Poblacion Las Navas Northern Samar</t>
         </is>
       </c>
       <c t="inlineStr" r="E44">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F44">
         <is>
-          <t>3/27/1987</t>
+          <t>9/22/1974</t>
         </is>
       </c>
       <c t="inlineStr" r="G44">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H44">
         <is>
-          <t>Head Mechanic</t>
+          <t>Sr. Tesd Specialist</t>
         </is>
       </c>
       <c t="inlineStr" r="I44">
         <is>
-          <t>Phil Auto Citi Services Inc</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J44">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K44">
         <is>
-          <t>Automotive Servicing NC I</t>
+          <t>Bread and Pastry Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L44">
         <is>
-          <t>ALTATS11801086426290021</t>
+          <t>TRSBPP20902086424290005</t>
         </is>
       </c>
       <c t="inlineStr" r="M44">
         <is>
-          <t>6/25/2026</t>
+          <t>10/24/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N44">
         <is>
-          <t>5/15/2029</t>
+          <t>5/26/2029</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c t="inlineStr" r="C45">
         <is>
-          <t>Creliza F. Gamay</t>
+          <t>Mikhaela Ysabelle Laplana Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D45">
         <is>
-          <t>Brgy. Poblacion Las Navas Northern Samar</t>
+          <t>Brgy. Mambajo City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E45">
@@ -3389,7 +3389,7 @@
       </c>
       <c t="inlineStr" r="F45">
         <is>
-          <t>9/22/1974</t>
+          <t>11/11/1996</t>
         </is>
       </c>
       <c t="inlineStr" r="G45">
@@ -3399,37 +3399,37 @@
       </c>
       <c t="inlineStr" r="H45">
         <is>
-          <t>Sr. Tesd Specialist</t>
+          <t>Job Order/ Bookkeeper</t>
         </is>
       </c>
       <c t="inlineStr" r="I45">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>Provincial Local Government Unit, Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J45">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Social, Community Development and Other Services</t>
         </is>
       </c>
       <c t="inlineStr" r="K45">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Bookkeeping NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L45">
         <is>
-          <t>TRSBPP20902086424290005</t>
+          <t>SOCBKP30703086424290004</t>
         </is>
       </c>
       <c t="inlineStr" r="M45">
         <is>
-          <t>10/24/2024</t>
+          <t>9/16/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N45">
         <is>
-          <t>5/26/2029</t>
+          <t>5/28/2029</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c t="inlineStr" r="C46">
         <is>
-          <t>Mikhaela Ysabelle Laplana Caores</t>
+          <t>Maria Normida Ordiz Caores</t>
         </is>
       </c>
       <c t="inlineStr" r="D46">
         <is>
-          <t>Brgy. Mambajo City of Maasin Southern Leyte</t>
+          <t>R. Kangleon Street Brgy. Mambajao,  City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E46">
@@ -3461,22 +3461,22 @@
       </c>
       <c t="inlineStr" r="F46">
         <is>
-          <t>11/11/1996</t>
+          <t>12/6/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G46">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H46">
         <is>
-          <t>Job Order/ Bookkeeper</t>
+          <t>Tesd Specialist 2</t>
         </is>
       </c>
       <c t="inlineStr" r="I46">
         <is>
-          <t>Provincial Local Government Unit, Southern Leyte</t>
+          <t>Tesda Southern Leyte Provincial Office</t>
         </is>
       </c>
       <c t="inlineStr" r="J46">
@@ -3491,12 +3491,12 @@
       </c>
       <c t="inlineStr" r="L46">
         <is>
-          <t>SOCBKP30703086424290004</t>
+          <t>SOCBKP30703086424290007</t>
         </is>
       </c>
       <c t="inlineStr" r="M46">
         <is>
-          <t>9/16/2024</t>
+          <t>10/24/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N46">
@@ -3518,52 +3518,52 @@
       </c>
       <c t="inlineStr" r="C47">
         <is>
-          <t>Maria Normida Ordiz Caores</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D47">
         <is>
-          <t>R. Kangleon Street Brgy. Mambajao,  City of Maasin Southern Leyte</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E47">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F47">
         <is>
-          <t>12/6/1969</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G47">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H47">
         <is>
-          <t>Tesd Specialist 2</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I47">
         <is>
-          <t>Tesda Southern Leyte Provincial Office</t>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J47">
         <is>
-          <t>Social, Community Development and Other Services</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K47">
         <is>
-          <t>Bookkeeping NC III</t>
+          <t>Cookery NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L47">
         <is>
-          <t>SOCBKP30703086424290007</t>
+          <t>TRSCOK21402086424290006</t>
         </is>
       </c>
       <c t="inlineStr" r="M47">
@@ -3573,7 +3573,7 @@
       </c>
       <c t="inlineStr" r="N47">
         <is>
-          <t>5/28/2029</t>
+          <t>6/2/2029</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c t="inlineStr" r="C48">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Roger . Ladica .</t>
         </is>
       </c>
       <c t="inlineStr" r="D48">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>Ponong Bato Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E48">
@@ -3605,12 +3605,12 @@
       </c>
       <c t="inlineStr" r="F48">
         <is>
-          <t>10/13/1993</t>
+          <t>3/2/1976</t>
         </is>
       </c>
       <c t="inlineStr" r="G48">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H48">
@@ -3620,32 +3620,32 @@
       </c>
       <c t="inlineStr" r="I48">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
+          <t>Bato Institute Of Science And Technology</t>
         </is>
       </c>
       <c t="inlineStr" r="J48">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K48">
         <is>
-          <t>Cookery NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L48">
         <is>
-          <t>TRSCOK21402086424290006</t>
+          <t>MEEEAW20602086424290002</t>
         </is>
       </c>
       <c t="inlineStr" r="M48">
         <is>
-          <t>10/24/2024</t>
+          <t>9/9/2024</t>
         </is>
       </c>
       <c t="inlineStr" r="N48">
         <is>
-          <t>6/2/2029</t>
+          <t>6/17/2029</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c t="inlineStr" r="C49">
         <is>
-          <t>Roger . Ladica .</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D49">
         <is>
-          <t>Ponong Bato Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E49">
@@ -3677,7 +3677,7 @@
       </c>
       <c t="inlineStr" r="F49">
         <is>
-          <t>3/2/1976</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G49">
@@ -3687,37 +3687,37 @@
       </c>
       <c t="inlineStr" r="H49">
         <is>
-          <t>Trainer</t>
+          <t>Farm Administrator</t>
         </is>
       </c>
       <c t="inlineStr" r="I49">
         <is>
-          <t>Bato Institute Of Science And Technology</t>
+          <t>Marsia Flora Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J49">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K49">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
+          <t>Agroentrepreneurship NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L49">
         <is>
-          <t>MEEEAW20602086424290002</t>
+          <t>AFFAGE21702086425290001</t>
         </is>
       </c>
       <c t="inlineStr" r="M49">
         <is>
-          <t>9/9/2024</t>
+          <t>1/15/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N49">
         <is>
-          <t>6/17/2029</t>
+          <t>7/1/2029</t>
         </is>
       </c>
     </row>
@@ -3734,62 +3734,62 @@
       </c>
       <c t="inlineStr" r="C50">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Shiela Bernaldez Diangco</t>
         </is>
       </c>
       <c t="inlineStr" r="D50">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Poblacion, Liloan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E50">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F50">
         <is>
-          <t>4/7/1969</t>
+          <t>6/16/1970</t>
         </is>
       </c>
       <c t="inlineStr" r="G50">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t>Farm Administrator</t>
+          <t>Teacher 2</t>
         </is>
       </c>
       <c t="inlineStr" r="I50">
         <is>
-          <t>Marsia Flora Integrated Farm</t>
+          <t>Liloan National Technical Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J50">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Garments</t>
         </is>
       </c>
       <c t="inlineStr" r="K50">
         <is>
-          <t>Agroentrepreneurship NC II</t>
+          <t>Dressmaking NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L50">
         <is>
-          <t>AFFAGE21702086425290001</t>
+          <t>GRMDRM20502086425290008</t>
         </is>
       </c>
       <c t="inlineStr" r="M50">
         <is>
-          <t>1/15/2025</t>
+          <t>8/22/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N50">
         <is>
-          <t>7/1/2029</t>
+          <t>7/9/2029</t>
         </is>
       </c>
     </row>
@@ -3806,22 +3806,22 @@
       </c>
       <c t="inlineStr" r="C51">
         <is>
-          <t>Shiela Bernaldez Diangco</t>
+          <t>Rhett Togonon Binghoy</t>
         </is>
       </c>
       <c t="inlineStr" r="D51">
         <is>
-          <t>Poblacion, Liloan Southern Leyte</t>
+          <t>Salog Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E51">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F51">
         <is>
-          <t>6/16/1970</t>
+          <t>2/24/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G51">
@@ -3831,37 +3831,37 @@
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t>Teacher 2</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I51">
         <is>
-          <t>Liloan National Technical Vocational High School</t>
+          <t>Pacific Vocational Training Center Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J51">
         <is>
-          <t>Garments</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K51">
         <is>
-          <t>Dressmaking NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
         </is>
       </c>
       <c t="inlineStr" r="L51">
         <is>
-          <t>GRMDRM20502086425290008</t>
+          <t>MEEEAW10601086426290016</t>
         </is>
       </c>
       <c t="inlineStr" r="M51">
         <is>
-          <t>8/22/2025</t>
+          <t>6/8/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N51">
         <is>
-          <t>7/9/2029</t>
+          <t>7/24/2029</t>
         </is>
       </c>
     </row>
@@ -3878,12 +3878,12 @@
       </c>
       <c t="inlineStr" r="C52">
         <is>
-          <t>Rhett Togonon Binghoy</t>
+          <t>Allen Dolorito Monter</t>
         </is>
       </c>
       <c t="inlineStr" r="D52">
         <is>
-          <t>Salog Hinunangan Southern Leyte</t>
+          <t>Asuncion City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E52">
@@ -3893,22 +3893,22 @@
       </c>
       <c t="inlineStr" r="F52">
         <is>
-          <t>2/24/1979</t>
+          <t>9/18/1990</t>
         </is>
       </c>
       <c t="inlineStr" r="G52">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H52">
         <is>
-          <t>Trainer</t>
+          <t>Freelancer</t>
         </is>
       </c>
       <c t="inlineStr" r="I52">
         <is>
-          <t>Pacific Vocational Training Center Inc.</t>
+          <t>Freelancer</t>
         </is>
       </c>
       <c t="inlineStr" r="J52">
@@ -3923,17 +3923,17 @@
       </c>
       <c t="inlineStr" r="L52">
         <is>
-          <t>MEEEAW10601086426290016</t>
+          <t>MEEEAW10601086425290015</t>
         </is>
       </c>
       <c t="inlineStr" r="M52">
         <is>
-          <t>6/8/2026</t>
+          <t>8/29/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N52">
         <is>
-          <t>7/24/2029</t>
+          <t>9/15/2029</t>
         </is>
       </c>
     </row>
@@ -3950,22 +3950,22 @@
       </c>
       <c t="inlineStr" r="C53">
         <is>
-          <t>Allen Dolorito Monter</t>
+          <t>Ma. Asuncion Bagolor Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D53">
         <is>
-          <t>Asuncion City of Maasin Southern Leyte</t>
+          <t>Brgy. Dongon City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E53">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F53">
         <is>
-          <t>9/18/1990</t>
+          <t>8/10/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G53">
@@ -3975,37 +3975,37 @@
       </c>
       <c t="inlineStr" r="H53">
         <is>
-          <t>Freelancer</t>
+          <t>Senior High School Teacher And College Teacher</t>
         </is>
       </c>
       <c t="inlineStr" r="I53">
         <is>
-          <t>Freelancer</t>
+          <t>The College Of Maasin, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J53">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K53">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC I</t>
+          <t>Cookery NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L53">
         <is>
-          <t>MEEEAW10601086425290015</t>
+          <t>TRSCOK21402086425290003</t>
         </is>
       </c>
       <c t="inlineStr" r="M53">
         <is>
-          <t>8/29/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N53">
         <is>
-          <t>9/15/2029</t>
+          <t>9/16/2029</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       </c>
       <c t="inlineStr" r="C54">
         <is>
-          <t>Ma. Asuncion Bagolor Mendoza</t>
+          <t>Lucia Misal Villarias</t>
         </is>
       </c>
       <c t="inlineStr" r="D54">
         <is>
-          <t>Brgy. Dongon City of Maasin Southern Leyte</t>
+          <t>Zone 1 Mangkaw Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E54">
@@ -4037,22 +4037,22 @@
       </c>
       <c t="inlineStr" r="F54">
         <is>
-          <t>8/10/1979</t>
+          <t>12/13/1959</t>
         </is>
       </c>
       <c t="inlineStr" r="G54">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t>Senior High School Teacher And College Teacher</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I54">
         <is>
-          <t>The College Of Maasin, Inc.</t>
+          <t>Ghrace Jhoy Technical And Vocational School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J54">
@@ -4067,17 +4067,17 @@
       </c>
       <c t="inlineStr" r="L54">
         <is>
-          <t>TRSCOK21402086425290003</t>
+          <t>TRSCOK21402086426290019</t>
         </is>
       </c>
       <c t="inlineStr" r="M54">
         <is>
-          <t>5/27/2025</t>
+          <t>6/8/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N54">
         <is>
-          <t>9/16/2029</t>
+          <t>10/20/2029</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c t="inlineStr" r="C55">
         <is>
-          <t>Lucia Misal Villarias</t>
+          <t>Creliza F. Gamay</t>
         </is>
       </c>
       <c t="inlineStr" r="D55">
         <is>
-          <t>Zone 1 Mangkaw Sogod Southern Leyte</t>
+          <t>Brgy. Poblacion Las Navas Northern Samar</t>
         </is>
       </c>
       <c t="inlineStr" r="E55">
@@ -4109,7 +4109,7 @@
       </c>
       <c t="inlineStr" r="F55">
         <is>
-          <t>12/13/1959</t>
+          <t>9/22/1974</t>
         </is>
       </c>
       <c t="inlineStr" r="G55">
@@ -4119,12 +4119,12 @@
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t>Trainer</t>
+          <t>Sr. Tesd Specialist</t>
         </is>
       </c>
       <c t="inlineStr" r="I55">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School Inc.</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J55">
@@ -4139,17 +4139,17 @@
       </c>
       <c t="inlineStr" r="L55">
         <is>
-          <t>TRSCOK21402086426290019</t>
+          <t>TRSCOK21402086425290004</t>
         </is>
       </c>
       <c t="inlineStr" r="M55">
         <is>
-          <t>6/8/2026</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N55">
         <is>
-          <t>10/20/2029</t>
+          <t>11/4/2029</t>
         </is>
       </c>
     </row>
@@ -4166,52 +4166,52 @@
       </c>
       <c t="inlineStr" r="C56">
         <is>
-          <t>Creliza F. Gamay</t>
+          <t>Cerecio Cabudbud Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D56">
         <is>
-          <t>Brgy. Poblacion Las Navas Northern Samar</t>
+          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E56">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F56">
         <is>
-          <t>9/22/1974</t>
+          <t>2/21/1960</t>
         </is>
       </c>
       <c t="inlineStr" r="G56">
         <is>
-          <t>College Graduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H56">
         <is>
-          <t>Sr. Tesd Specialist</t>
+          <t>Head Teacher Iii</t>
         </is>
       </c>
       <c t="inlineStr" r="I56">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>Villa Jacinta National Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J56">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K56">
         <is>
-          <t>Cookery NC II</t>
+          <t>Tile Setting NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L56">
         <is>
-          <t>TRSCOK21402086425290004</t>
+          <t>CONTIL21802086425290007</t>
         </is>
       </c>
       <c t="inlineStr" r="M56">
@@ -4221,7 +4221,7 @@
       </c>
       <c t="inlineStr" r="N56">
         <is>
-          <t>11/4/2029</t>
+          <t>11/13/2029</t>
         </is>
       </c>
     </row>
@@ -4238,12 +4238,12 @@
       </c>
       <c t="inlineStr" r="C57">
         <is>
-          <t>Cerecio Cabudbud Mendoza</t>
+          <t>Eduardo Lora Bosque</t>
         </is>
       </c>
       <c t="inlineStr" r="D57">
         <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
+          <t>San Rafael City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E57">
@@ -4253,47 +4253,47 @@
       </c>
       <c t="inlineStr" r="F57">
         <is>
-          <t>2/21/1960</t>
+          <t>3/27/1987</t>
         </is>
       </c>
       <c t="inlineStr" r="G57">
         <is>
-          <t>Masteral</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H57">
         <is>
-          <t>Head Teacher Iii</t>
+          <t>Head Mechanic</t>
         </is>
       </c>
       <c t="inlineStr" r="I57">
         <is>
-          <t>Villa Jacinta National Vocational High School</t>
+          <t>Phil - Auto Citi Services Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J57">
         <is>
-          <t>Construction</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K57">
         <is>
-          <t>Tile Setting NC II</t>
+          <t>Driving NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L57">
         <is>
-          <t>CONTIL21802086425290007</t>
+          <t>ALTDRV20402086425300002</t>
         </is>
       </c>
       <c t="inlineStr" r="M57">
         <is>
-          <t>6/18/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N57">
         <is>
-          <t>11/13/2029</t>
+          <t>1/21/2030</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4310,12 @@
       </c>
       <c t="inlineStr" r="C58">
         <is>
-          <t>Eduardo Lora Bosque</t>
+          <t>Cerecio Cabudbud Mendoza</t>
         </is>
       </c>
       <c t="inlineStr" r="D58">
         <is>
-          <t>San Rafael City of Maasin Southern Leyte</t>
+          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E58">
@@ -4325,47 +4325,47 @@
       </c>
       <c t="inlineStr" r="F58">
         <is>
-          <t>3/27/1987</t>
+          <t>2/21/1960</t>
         </is>
       </c>
       <c t="inlineStr" r="G58">
         <is>
-          <t>College Undergraduate</t>
+          <t>Masteral</t>
         </is>
       </c>
       <c t="inlineStr" r="H58">
         <is>
-          <t>Head Mechanic</t>
+          <t>Head Teacher Iii</t>
         </is>
       </c>
       <c t="inlineStr" r="I58">
         <is>
-          <t>Phil - Auto Citi Services Inc.</t>
+          <t>Villa Jacinta National Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J58">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K58">
         <is>
-          <t>Driving NC II</t>
+          <t>Carpentry NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L58">
         <is>
-          <t>ALTDRV20402086425300002</t>
+          <t>CONCAR21802086425300005</t>
         </is>
       </c>
       <c t="inlineStr" r="M58">
         <is>
-          <t>5/27/2025</t>
+          <t>6/18/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N58">
         <is>
-          <t>1/21/2030</t>
+          <t>1/27/2030</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c t="inlineStr" r="I59">
         <is>
-          <t>Villa Jacinta National Vocational High School</t>
+          <t>Villa Jacinta Nationalvocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J59">
@@ -4422,12 +4422,12 @@
       </c>
       <c t="inlineStr" r="K59">
         <is>
-          <t>Carpentry NC II</t>
+          <t>Masonry NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L59">
         <is>
-          <t>CONCAR21802086425300005</t>
+          <t>CONMAS21802086425300006</t>
         </is>
       </c>
       <c t="inlineStr" r="M59">
@@ -4454,62 +4454,62 @@
       </c>
       <c t="inlineStr" r="C60">
         <is>
-          <t>Cerecio Cabudbud Mendoza</t>
+          <t>Marie Fe Matunog Adan</t>
         </is>
       </c>
       <c t="inlineStr" r="D60">
         <is>
-          <t>Lower Villa Jacinta, Macrohon Southern Leyte</t>
+          <t>Purok B Bangcas A Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E60">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F60">
         <is>
-          <t>2/21/1960</t>
+          <t>5/26/1989</t>
         </is>
       </c>
       <c t="inlineStr" r="G60">
         <is>
-          <t>Masteral</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H60">
         <is>
-          <t>Head Teacher Iii</t>
+          <t>Trainer/ Admin Support Staff</t>
         </is>
       </c>
       <c t="inlineStr" r="I60">
         <is>
-          <t>Villa Jacinta Nationalvocational High School</t>
+          <t>Ssm Integrated Farm</t>
         </is>
       </c>
       <c t="inlineStr" r="J60">
         <is>
-          <t>Construction</t>
+          <t>Agriculture, Forestry and Fishery</t>
         </is>
       </c>
       <c t="inlineStr" r="K60">
         <is>
-          <t>Masonry NC II</t>
+          <t>Organic Agriculture Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L60">
         <is>
-          <t>CONMAS21802086425300006</t>
+          <t>AFFOAP21202086425300011</t>
         </is>
       </c>
       <c t="inlineStr" r="M60">
         <is>
-          <t>6/18/2025</t>
+          <t>8/22/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N60">
         <is>
-          <t>1/27/2030</t>
+          <t>3/3/2030</t>
         </is>
       </c>
     </row>
@@ -4526,22 +4526,22 @@
       </c>
       <c t="inlineStr" r="C61">
         <is>
-          <t>Marie Fe Matunog Adan</t>
+          <t>Jordan Morata Catubig</t>
         </is>
       </c>
       <c t="inlineStr" r="D61">
         <is>
-          <t>Purok B Bangcas A Hinunangan Southern Leyte</t>
+          <t>M. H. Del Pilar Taliwa Malitbog Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E61">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F61">
         <is>
-          <t>5/26/1989</t>
+          <t>9/8/1977</t>
         </is>
       </c>
       <c t="inlineStr" r="G61">
@@ -4551,37 +4551,37 @@
       </c>
       <c t="inlineStr" r="H61">
         <is>
-          <t>Trainer/ Admin Support Staff</t>
+          <t>Electricain</t>
         </is>
       </c>
       <c t="inlineStr" r="I61">
         <is>
-          <t>Ssm Integrated Farm</t>
+          <t>Southern Leyte Electric Cooperative, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J61">
         <is>
-          <t>Agriculture, Forestry and Fishery</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K61">
         <is>
-          <t>Organic Agriculture Production NC II</t>
+          <t>Electrical Installation and Maintenance NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L61">
         <is>
-          <t>AFFOAP21202086425300011</t>
+          <t>ELCEIM21502086426300003</t>
         </is>
       </c>
       <c t="inlineStr" r="M61">
         <is>
-          <t>8/22/2025</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N61">
         <is>
-          <t>3/3/2030</t>
+          <t>3/5/2030</t>
         </is>
       </c>
     </row>
@@ -4598,22 +4598,22 @@
       </c>
       <c t="inlineStr" r="C62">
         <is>
-          <t>Jordan Morata Catubig</t>
+          <t>Ma. Luisa Garong Terre</t>
         </is>
       </c>
       <c t="inlineStr" r="D62">
         <is>
-          <t>M. H. Del Pilar Taliwa Malitbog Southern Leyte</t>
+          <t>Ibarra City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E62">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F62">
         <is>
-          <t>9/8/1977</t>
+          <t>5/18/1976</t>
         </is>
       </c>
       <c t="inlineStr" r="G62">
@@ -4623,12 +4623,12 @@
       </c>
       <c t="inlineStr" r="H62">
         <is>
-          <t>Electricain</t>
+          <t>C Omputer Iinstructor/ Processor</t>
         </is>
       </c>
       <c t="inlineStr" r="I62">
         <is>
-          <t>Southern Leyte Electric Cooperative, Inc.</t>
+          <t>St. Thiomas Aquimas College</t>
         </is>
       </c>
       <c t="inlineStr" r="J62">
@@ -4638,22 +4638,22 @@
       </c>
       <c t="inlineStr" r="K62">
         <is>
-          <t>Electrical Installation and Maintenance NC II</t>
+          <t>Computer Systems Servicing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L62">
         <is>
-          <t>ELCEIM21502086426300003</t>
+          <t>ELCCSS21302086425300014</t>
         </is>
       </c>
       <c t="inlineStr" r="M62">
         <is>
-          <t>1/23/2026</t>
+          <t>8/29/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="N62">
         <is>
-          <t>3/5/2030</t>
+          <t>4/20/2030</t>
         </is>
       </c>
     </row>
@@ -4670,62 +4670,62 @@
       </c>
       <c t="inlineStr" r="C63">
         <is>
-          <t>Ma. Luisa Garong Terre</t>
+          <t>Amiel Lora Bosque</t>
         </is>
       </c>
       <c t="inlineStr" r="D63">
         <is>
-          <t>Ibarra City of Maasin Southern Leyte</t>
+          <t>Brgy. San Rafael City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E63">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F63">
         <is>
-          <t>5/18/1976</t>
+          <t>10/11/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G63">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t>C Omputer Iinstructor/ Processor</t>
+          <t>Welder</t>
         </is>
       </c>
       <c t="inlineStr" r="I63">
         <is>
-          <t>St. Thiomas Aquimas College</t>
+          <t>Ac Marine Services</t>
         </is>
       </c>
       <c t="inlineStr" r="J63">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K63">
         <is>
-          <t>Computer Systems Servicing NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L63">
         <is>
-          <t>ELCCSS21302086425300014</t>
+          <t>MEEEAW20602086426300002</t>
         </is>
       </c>
       <c t="inlineStr" r="M63">
         <is>
-          <t>8/29/2025</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N63">
         <is>
-          <t>4/20/2030</t>
+          <t>8/28/2030</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c t="inlineStr" r="C64">
         <is>
-          <t>Amiel Lora Bosque</t>
+          <t>John Francisco Dalina Alvar</t>
         </is>
       </c>
       <c t="inlineStr" r="D64">
         <is>
-          <t>Brgy. San Rafael City of Maasin Southern Leyte</t>
+          <t>Tinago Tomas Oppus Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E64">
@@ -4757,47 +4757,47 @@
       </c>
       <c t="inlineStr" r="F64">
         <is>
-          <t>10/11/1983</t>
+          <t>10/13/1993</t>
         </is>
       </c>
       <c t="inlineStr" r="G64">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H64">
         <is>
-          <t>Welder</t>
+          <t>Head Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I64">
         <is>
-          <t>Ac Marine Services</t>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J64">
         <is>
-          <t>Metals and Engineering</t>
+          <t>Construction</t>
         </is>
       </c>
       <c t="inlineStr" r="K64">
         <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
+          <t>Masonry NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L64">
         <is>
-          <t>MEEEAW20602086426300002</t>
+          <t>CONMAS21802086426300006</t>
         </is>
       </c>
       <c t="inlineStr" r="M64">
         <is>
-          <t>1/23/2026</t>
+          <t>2/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N64">
         <is>
-          <t>8/28/2030</t>
+          <t>10/9/2030</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c t="inlineStr" r="C65">
         <is>
-          <t>John Francisco Dalina Alvar</t>
+          <t>Ranulfo Datoy Kuizon Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D65">
         <is>
-          <t>Tinago Tomas Oppus Southern Leyte</t>
+          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E65">
@@ -4829,22 +4829,22 @@
       </c>
       <c t="inlineStr" r="F65">
         <is>
-          <t>10/13/1993</t>
+          <t>6/26/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G65">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H65">
         <is>
-          <t>Head Trainer</t>
+          <t>Administrative Assistant 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I65">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J65">
@@ -4854,22 +4854,22 @@
       </c>
       <c t="inlineStr" r="K65">
         <is>
-          <t>Masonry NC II</t>
+          <t>Tile Setting NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L65">
         <is>
-          <t>CONMAS21802086426300006</t>
+          <t>CONTIL21802086426300001</t>
         </is>
       </c>
       <c t="inlineStr" r="M65">
         <is>
-          <t>2/20/2026</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N65">
         <is>
-          <t>10/9/2030</t>
+          <t>10/14/2030</t>
         </is>
       </c>
     </row>
@@ -4886,12 +4886,12 @@
       </c>
       <c t="inlineStr" r="C66">
         <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
+          <t>Joedee Mark . Rodriguez</t>
         </is>
       </c>
       <c t="inlineStr" r="D66">
         <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
+          <t>Brgy. San Jose Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E66">
@@ -4901,47 +4901,47 @@
       </c>
       <c t="inlineStr" r="F66">
         <is>
-          <t>6/26/1983</t>
+          <t>1/20/1995</t>
         </is>
       </c>
       <c t="inlineStr" r="G66">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H66">
         <is>
-          <t>Administrative Assistant 3</t>
+          <t>Ac Manager</t>
         </is>
       </c>
       <c t="inlineStr" r="I66">
         <is>
-          <t>Ptc - Southern Leyte</t>
+          <t>Southern Leyte Stete University</t>
         </is>
       </c>
       <c t="inlineStr" r="J66">
         <is>
-          <t>Construction</t>
+          <t>Electrical and Electronics</t>
         </is>
       </c>
       <c t="inlineStr" r="K66">
         <is>
-          <t>Tile Setting NC II</t>
+          <t>Computer Systems Servicing NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L66">
         <is>
-          <t>CONTIL21802086426300001</t>
+          <t>ELCCSS21302086426300022</t>
         </is>
       </c>
       <c t="inlineStr" r="M66">
         <is>
-          <t>1/23/2026</t>
+          <t>6/25/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N66">
         <is>
-          <t>10/14/2030</t>
+          <t>10/22/2030</t>
         </is>
       </c>
     </row>
@@ -4958,22 +4958,22 @@
       </c>
       <c t="inlineStr" r="C67">
         <is>
-          <t>Joedee Mark . Rodriguez</t>
+          <t>Michel Tingcoy Pata</t>
         </is>
       </c>
       <c t="inlineStr" r="D67">
         <is>
-          <t>Brgy. San Jose Sogod Southern Leyte</t>
+          <t>Mahayahay Bontoc Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E67">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c t="inlineStr" r="F67">
         <is>
-          <t>1/20/1995</t>
+          <t>8/24/1980</t>
         </is>
       </c>
       <c t="inlineStr" r="G67">
@@ -4983,37 +4983,37 @@
       </c>
       <c t="inlineStr" r="H67">
         <is>
-          <t>Ac Manager</t>
+          <t>Teacher 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I67">
         <is>
-          <t>Southern Leyte Stete University</t>
+          <t>Villa Jacinta Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J67">
         <is>
-          <t>Electrical and Electronics</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K67">
         <is>
-          <t>Computer Systems Servicing NC II</t>
+          <t>Bread and Pastry Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L67">
         <is>
-          <t>ELCCSS21302086426300022</t>
+          <t>TRSBPP20902086426300014</t>
         </is>
       </c>
       <c t="inlineStr" r="M67">
         <is>
-          <t>6/25/2026</t>
+          <t>5/11/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N67">
         <is>
-          <t>10/22/2030</t>
+          <t>12/3/2030</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5030,12 @@
       </c>
       <c t="inlineStr" r="C68">
         <is>
-          <t>Michel Tingcoy Pata</t>
+          <t>Lucia Misal Villarias</t>
         </is>
       </c>
       <c t="inlineStr" r="D68">
         <is>
-          <t>Mahayahay Bontoc Southern Leyte</t>
+          <t>Zone 1 Mangkaw Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E68">
@@ -5045,7 +5045,7 @@
       </c>
       <c t="inlineStr" r="F68">
         <is>
-          <t>8/24/1980</t>
+          <t>12/13/1959</t>
         </is>
       </c>
       <c t="inlineStr" r="G68">
@@ -5055,12 +5055,12 @@
       </c>
       <c t="inlineStr" r="H68">
         <is>
-          <t>Teacher 3</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I68">
         <is>
-          <t>Villa Jacinta Vocational High School</t>
+          <t>Ghrace Jhoy Technical Educational School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J68">
@@ -5070,12 +5070,12 @@
       </c>
       <c t="inlineStr" r="K68">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Food and Beverage Services NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L68">
         <is>
-          <t>TRSBPP20902086426300014</t>
+          <t>TRSFBS21302086426300013</t>
         </is>
       </c>
       <c t="inlineStr" r="M68">
@@ -5085,7 +5085,7 @@
       </c>
       <c t="inlineStr" r="N68">
         <is>
-          <t>12/3/2030</t>
+          <t>12/4/2030</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c t="inlineStr" r="I69">
         <is>
-          <t>Ghrace Jhoy Technical Educational School Inc.</t>
+          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J69">
@@ -5142,17 +5142,17 @@
       </c>
       <c t="inlineStr" r="K69">
         <is>
-          <t>Food and Beverage Services NC II</t>
+          <t>Housekeeping NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L69">
         <is>
-          <t>TRSFBS21302086426300013</t>
+          <t>TRSHSK21302086426300023</t>
         </is>
       </c>
       <c t="inlineStr" r="M69">
         <is>
-          <t>5/11/2026</t>
+          <t>9/2/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N69">
@@ -5174,12 +5174,12 @@
       </c>
       <c t="inlineStr" r="C70">
         <is>
-          <t>Lucia Misal Villarias</t>
+          <t>Archiel Sacurom  Amora</t>
         </is>
       </c>
       <c t="inlineStr" r="D70">
         <is>
-          <t>Zone 1 Mangkaw Sogod Southern Leyte</t>
+          <t>Consolacion Sogod Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E70">
@@ -5189,7 +5189,7 @@
       </c>
       <c t="inlineStr" r="F70">
         <is>
-          <t>12/13/1959</t>
+          <t>11/9/1996</t>
         </is>
       </c>
       <c t="inlineStr" r="G70">
@@ -5199,37 +5199,37 @@
       </c>
       <c t="inlineStr" r="H70">
         <is>
-          <t>Trainer</t>
+          <t>Trainer/ Registrar</t>
         </is>
       </c>
       <c t="inlineStr" r="I70">
         <is>
-          <t>Ghrace Jhoy Technical And Vocational School, Inc.</t>
+          <t>Arc Tutorial Learning Services Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J70">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Social, Community Development and Other Services</t>
         </is>
       </c>
       <c t="inlineStr" r="K70">
         <is>
-          <t>Housekeeping NC II</t>
+          <t>Early Childhood Care and Development Services NC III</t>
         </is>
       </c>
       <c t="inlineStr" r="L70">
         <is>
-          <t>TRSHSK21302086426300023</t>
+          <t>SOCECD32503086426300012</t>
         </is>
       </c>
       <c t="inlineStr" r="M70">
         <is>
-          <t>9/2/2026</t>
+          <t>5/11/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N70">
         <is>
-          <t>12/4/2030</t>
+          <t>12/14/2030</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5246,12 @@
       </c>
       <c t="inlineStr" r="C71">
         <is>
-          <t>Archiel Sacurom  Amora</t>
+          <t>Brenda Napuli Balogo</t>
         </is>
       </c>
       <c t="inlineStr" r="D71">
         <is>
-          <t>Consolacion Sogod Southern Leyte</t>
+          <t>R. Garces Street Brgy. Tunga-tunga City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E71">
@@ -5261,7 +5261,7 @@
       </c>
       <c t="inlineStr" r="F71">
         <is>
-          <t>11/9/1996</t>
+          <t>5/23/1958</t>
         </is>
       </c>
       <c t="inlineStr" r="G71">
@@ -5271,27 +5271,27 @@
       </c>
       <c t="inlineStr" r="H71">
         <is>
-          <t>Trainer/ Registrar</t>
+          <t>Teacher 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I71">
         <is>
-          <t>Arc Tutorial Learning Services Inc.</t>
+          <t>Villa Jacinta National Vocational High School</t>
         </is>
       </c>
       <c t="inlineStr" r="J71">
         <is>
-          <t>Social, Community Development and Other Services</t>
+          <t>Tourism (Hotel and Restaurant)</t>
         </is>
       </c>
       <c t="inlineStr" r="K71">
         <is>
-          <t>Early Childhood Care and Development Services NC III</t>
+          <t>Bread and Pastry Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L71">
         <is>
-          <t>SOCECD32503086426300012</t>
+          <t>TRSBPP20902086426310011</t>
         </is>
       </c>
       <c t="inlineStr" r="M71">
@@ -5301,7 +5301,7 @@
       </c>
       <c t="inlineStr" r="N71">
         <is>
-          <t>12/14/2030</t>
+          <t>1/12/2031</t>
         </is>
       </c>
     </row>
@@ -5318,37 +5318,37 @@
       </c>
       <c t="inlineStr" r="C72">
         <is>
-          <t>Brenda Napuli Balogo</t>
+          <t>Joel Piso Paler</t>
         </is>
       </c>
       <c t="inlineStr" r="D72">
         <is>
-          <t>R. Garces Street Brgy. Tunga-tunga City of Maasin Southern Leyte</t>
+          <t>Hitawos Bontoc Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E72">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c t="inlineStr" r="F72">
         <is>
-          <t>5/23/1958</t>
+          <t>4/18/2001</t>
         </is>
       </c>
       <c t="inlineStr" r="G72">
         <is>
-          <t>College Graduate</t>
+          <t>Post Secondary Non-Tertiary/Technical Vocational Course Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H72">
         <is>
-          <t>Teacher 3</t>
+          <t>Instructor</t>
         </is>
       </c>
       <c t="inlineStr" r="I72">
         <is>
-          <t>Villa Jacinta National Vocational High School</t>
+          <t>Farmfinity Resort</t>
         </is>
       </c>
       <c t="inlineStr" r="J72">
@@ -5358,22 +5358,22 @@
       </c>
       <c t="inlineStr" r="K72">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Food and Beverage Services NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L72">
         <is>
-          <t>TRSBPP20902086426310011</t>
+          <t>TRSFBS21302086426310008</t>
         </is>
       </c>
       <c t="inlineStr" r="M72">
         <is>
-          <t>5/11/2026</t>
+          <t>2/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N72">
         <is>
-          <t>1/12/2031</t>
+          <t>2/18/2031</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c t="inlineStr" r="C73">
         <is>
-          <t>Joel Piso Paler</t>
+          <t>Fedencio Cabug-os Alinsub Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D73">
         <is>
-          <t>Hitawos Bontoc Southern Leyte</t>
+          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E73">
@@ -5405,22 +5405,22 @@
       </c>
       <c t="inlineStr" r="F73">
         <is>
-          <t>4/18/2001</t>
+          <t>4/7/1969</t>
         </is>
       </c>
       <c t="inlineStr" r="G73">
         <is>
-          <t>Post Secondary Non-Tertiary/Technical Vocational Course Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H73">
         <is>
-          <t>Instructor</t>
+          <t>School Administrator</t>
         </is>
       </c>
       <c t="inlineStr" r="I73">
         <is>
-          <t>Farmfinity Resort</t>
+          <t>Marsia Fiona Agro - Industrial School Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J73">
@@ -5430,12 +5430,12 @@
       </c>
       <c t="inlineStr" r="K73">
         <is>
-          <t>Food and Beverage Services NC II</t>
+          <t>Bread and Pastry Production NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L73">
         <is>
-          <t>TRSFBS21302086426310008</t>
+          <t>TRSBPP20902086426310009</t>
         </is>
       </c>
       <c t="inlineStr" r="M73">
@@ -5462,12 +5462,12 @@
       </c>
       <c t="inlineStr" r="C74">
         <is>
-          <t>Fedencio Cabug-os Alinsub Jr.</t>
+          <t>Rhett Togonon Binghoy</t>
         </is>
       </c>
       <c t="inlineStr" r="D74">
         <is>
-          <t>Purok 5 Barangay Bactul Ii City of Maasin Southern Leyte</t>
+          <t>Salog Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E74">
@@ -5477,22 +5477,22 @@
       </c>
       <c t="inlineStr" r="F74">
         <is>
-          <t>4/7/1969</t>
+          <t>2/24/1979</t>
         </is>
       </c>
       <c t="inlineStr" r="G74">
         <is>
-          <t>College Undergraduate</t>
+          <t>College Graduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H74">
         <is>
-          <t>School Administrator</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c t="inlineStr" r="I74">
         <is>
-          <t>Marsia Fiona Agro - Industrial School Inc.</t>
+          <t>Pacific Vocational Training Center Inc.</t>
         </is>
       </c>
       <c t="inlineStr" r="J74">
@@ -5502,22 +5502,22 @@
       </c>
       <c t="inlineStr" r="K74">
         <is>
-          <t>Bread and Pastry Production NC II</t>
+          <t>Cookery NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L74">
         <is>
-          <t>TRSBPP20902086426310009</t>
+          <t>TRSCOK21402086426310015</t>
         </is>
       </c>
       <c t="inlineStr" r="M74">
         <is>
-          <t>2/20/2026</t>
+          <t>5/11/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N74">
         <is>
-          <t>2/18/2031</t>
+          <t>4/7/2031</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5534,12 @@
       </c>
       <c t="inlineStr" r="C75">
         <is>
-          <t>Rhett Togonon Binghoy</t>
+          <t>Ranulfo Datoy Kuizon Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="D75">
         <is>
-          <t>Salog Hinunangan Southern Leyte</t>
+          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="E75">
@@ -5549,47 +5549,47 @@
       </c>
       <c t="inlineStr" r="F75">
         <is>
-          <t>2/24/1979</t>
+          <t>6/26/1983</t>
         </is>
       </c>
       <c t="inlineStr" r="G75">
         <is>
-          <t>College Graduate</t>
+          <t>College Undergraduate</t>
         </is>
       </c>
       <c t="inlineStr" r="H75">
         <is>
-          <t>Trainer</t>
+          <t>Administrative Assistant 3</t>
         </is>
       </c>
       <c t="inlineStr" r="I75">
         <is>
-          <t>Pacific Vocational Training Center Inc.</t>
+          <t>Ptc - Southern Leyte</t>
         </is>
       </c>
       <c t="inlineStr" r="J75">
         <is>
-          <t>Tourism (Hotel and Restaurant)</t>
+          <t>Automotive and Land Transportation</t>
         </is>
       </c>
       <c t="inlineStr" r="K75">
         <is>
-          <t>Cookery NC II</t>
+          <t>Driving NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L75">
         <is>
-          <t>TRSCOK21402086426310015</t>
+          <t>ALTDRV20402086426310017</t>
         </is>
       </c>
       <c t="inlineStr" r="M75">
         <is>
-          <t>5/11/2026</t>
+          <t>6/8/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N75">
         <is>
-          <t>4/7/2031</t>
+          <t>4/20/2031</t>
         </is>
       </c>
     </row>
@@ -5641,97 +5641,25 @@
       </c>
       <c t="inlineStr" r="J76">
         <is>
-          <t>Automotive and Land Transportation</t>
+          <t>Metals and Engineering</t>
         </is>
       </c>
       <c t="inlineStr" r="K76">
         <is>
-          <t>Driving NC II</t>
+          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
         </is>
       </c>
       <c t="inlineStr" r="L76">
         <is>
-          <t>ALTDRV20402086426310017</t>
+          <t>MEEEAW20602086426310018</t>
         </is>
       </c>
       <c t="inlineStr" r="M76">
         <is>
-          <t>6/8/2026</t>
+          <t>6/9/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="N76">
-        <is>
-          <t>4/20/2031</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c t="inlineStr" r="A77">
-        <is>
-          <t>Region VIII - Eastern Visayas</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B77">
-        <is>
-          <t>Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C77">
-        <is>
-          <t>Ranulfo Datoy Kuizon Jr.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="D77">
-        <is>
-          <t>Brgy. Pondol,  Hinunangan Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E77">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F77">
-        <is>
-          <t>6/26/1983</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G77">
-        <is>
-          <t>College Undergraduate</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H77">
-        <is>
-          <t>Administrative Assistant 3</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I77">
-        <is>
-          <t>Ptc - Southern Leyte</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J77">
-        <is>
-          <t>Metals and Engineering</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="K77">
-        <is>
-          <t>Shielded Metal Arc Welding (SMAW) NC II</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L77">
-        <is>
-          <t>MEEEAW20602086426310018</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M77">
-        <is>
-          <t>6/9/2026</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N77">
         <is>
           <t>4/20/2031</t>
         </is>
